--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>91.56999999999999</v>
+        <v>90.06</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>104</v>
+        <v>102.89</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>92.59</v>
+        <v>90.88</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>105.23</v>
+        <v>103.93</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99.19</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>109.7</v>
+        <v>110.31</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>101.71</v>
+        <v>101.95</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>112.5</v>
+        <v>112.97</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>83.66</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>91.89</v>
+        <v>92.28</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>86.53</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>95.03</v>
+        <v>95.26000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>88.56999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>97.98999999999999</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>95.86</v>
+        <v>96.72</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>106.14</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>81.25</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>88.93000000000001</v>
+        <v>87.66</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>95.29000000000001</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>104.27</v>
+        <v>102.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Mar 2026</t>
+          <t>Data through: Apr 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5793,6 +5793,26 @@
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F253" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5804,7 +5824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10610,8 +10630,27 @@
         <v>88.52</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B252">
+  <conditionalFormatting sqref="B2:B253">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10623,7 +10662,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C252">
+  <conditionalFormatting sqref="C2:C253">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10635,7 +10674,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D252">
+  <conditionalFormatting sqref="D2:D253">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10647,7 +10686,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E252">
+  <conditionalFormatting sqref="E2:E253">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>90.06</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>102.89</v>
+        <v>101.24</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>90.88</v>
+        <v>90.47</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>103.93</v>
+        <v>103.06</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99.56999999999999</v>
+        <v>97.48</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>110.31</v>
+        <v>108.14</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>101.95</v>
+        <v>100.76</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>112.97</v>
+        <v>111.85</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84.01000000000001</v>
+        <v>84.19</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>92.28</v>
+        <v>92.48</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>86.70999999999999</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>95.26000000000001</v>
+        <v>96.42</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>89.52</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>98.93000000000001</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>96.72</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>106.97</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>79.95999999999999</v>
+        <v>80.34</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.66</v>
+        <v>87.97</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.34999999999999</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>102.35</v>
+        <v>103.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Apr 2026</t>
+          <t>Data through: May 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>537.86</v>
+        <v>545.26</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>687.21</v>
+        <v>696.66</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>137.54</v>
+        <v>139.44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>195.86</v>
+        <v>198.56</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>201.27</v>
+        <v>204.04</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>186.29</v>
+        <v>188.85</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>245.14</v>
+        <v>248.52</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>120.12</v>
+        <v>121.77</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>135.2</v>
+        <v>137.06</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>142.44</v>
+        <v>144.4</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>176.81</v>
+        <v>179.25</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>99.48999999999999</v>
+        <v>100.86</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102.3</v>
+        <v>103.71</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>73.78</v>
+        <v>74.8</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>63.4</v>
+        <v>64.27</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>69.36</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55.58</v>
+        <v>56.34</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>61.27</v>
+        <v>62.11</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>48.52</v>
+        <v>49.19</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>55.61</v>
+        <v>56.37</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>56.69</v>
+        <v>57.47</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>57.51</v>
+        <v>58.3</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.07</v>
+        <v>57.86</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>80.44</v>
+        <v>81.55</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>69.61</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>88.61</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>80.89</v>
+        <v>82</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>115.38</v>
+        <v>116.97</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>58.8</v>
+        <v>59.61</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>66.59</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.76</v>
+        <v>64.64</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>69.23</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.08</v>
+        <v>57.87</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>61.42</v>
+        <v>62.26</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>68.56</v>
+        <v>69.5</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>73.91</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>78.84</v>
+        <v>79.92</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>88.31999999999999</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>112.76</v>
+        <v>114.31</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>84.63</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>91</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>121.37</v>
+        <v>123.04</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>136.5</v>
+        <v>138.37</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>109.73</v>
+        <v>111.24</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>119.6</v>
+        <v>121.25</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>128.18</v>
+        <v>129.94</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>131.67</v>
+        <v>133.48</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>163.45</v>
+        <v>165.7</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>189.83</v>
+        <v>192.44</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>80.05</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>77.29000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>82.29000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>55.5</v>
+        <v>56.26</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>80.37</v>
+        <v>81.48</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>98.13</v>
+        <v>99.48</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>76.38</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>95.31</v>
+        <v>96.62</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>90.70999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>108.85</v>
+        <v>110.34</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>89.84</v>
+        <v>91.08</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>110.03</v>
+        <v>111.54</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>87.44</v>
+        <v>88.64</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>101.62</v>
+        <v>103.02</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>107.31</v>
+        <v>108.79</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>110.45</v>
+        <v>111.97</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>88.23</v>
+        <v>89.44</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>99.75</v>
+        <v>101.12</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.68</v>
+        <v>48.34</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>47.52</v>
+        <v>48.18</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>85.98</v>
+        <v>87.17</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>95.34</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>68.48</v>
+        <v>69.42</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>83.38</v>
+        <v>84.53</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>71.64</v>
+        <v>72.63</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>87.87</v>
+        <v>89.08</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>79.19</v>
+        <v>80.28</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>95.76000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>51.46</v>
+        <v>52.17</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>59.89</v>
+        <v>60.71</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>123.29</v>
+        <v>124.99</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>186.98</v>
+        <v>189.56</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.06</v>
+        <v>61.9</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>99.86</v>
+        <v>101.23</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>56.98</v>
+        <v>57.76</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>68.3</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>108.07</v>
+        <v>109.56</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>98.59</v>
+        <v>99.95</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>72.92</v>
+        <v>73.92</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>77.94</v>
+        <v>79.02</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>270.11</v>
+        <v>273.83</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>453.84</v>
+        <v>460.08</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.11</v>
+        <v>40.66</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.08</v>
+        <v>49.76</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>32.88</v>
+        <v>33.33</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.29</v>
+        <v>43.89</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.13</v>
+        <v>33.59</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.35</v>
+        <v>42.94</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>39.62</v>
+        <v>40.16</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.32</v>
+        <v>46.96</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>51.7</v>
+        <v>52.41</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>58.46</v>
+        <v>59.27</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>44.62</v>
+        <v>45.24</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>49.65</v>
+        <v>50.33</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.47</v>
+        <v>36.97</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.37</v>
+        <v>31.8</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>39.75</v>
+        <v>40.3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>36.98</v>
+        <v>37.49</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>39.67</v>
+        <v>40.22</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>86.09</v>
+        <v>87.27</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>61.25</v>
+        <v>62.09</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>46.59</v>
+        <v>47.23</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52</v>
+        <v>52.72</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>45.44</v>
+        <v>46.06</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.14</v>
+        <v>51.84</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>97.26000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>41.68</v>
+        <v>42.25</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.08</v>
+        <v>31.51</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>35.85</v>
+        <v>36.34</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.13</v>
+        <v>27.5</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>27.75</v>
+        <v>28.14</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>40.47</v>
+        <v>41.03</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>57.47</v>
+        <v>58.26</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>24.91</v>
+        <v>25.25</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.55</v>
+        <v>26.91</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>38.51</v>
+        <v>39.04</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.08</v>
+        <v>42.66</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.4</v>
+        <v>42.98</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>46.47</v>
+        <v>47.11</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>37.94</v>
+        <v>38.46</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>39.98</v>
+        <v>40.53</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.24</v>
+        <v>39.78</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>40.69</v>
+        <v>41.25</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>56.45</v>
+        <v>57.23</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>59.46</v>
+        <v>60.28</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>42.44</v>
+        <v>43.02</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.02</v>
+        <v>47.67</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.34</v>
+        <v>47.99</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>71.34999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.37</v>
+        <v>39.91</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.29</v>
+        <v>50.98</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.2</v>
+        <v>38.72</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.26</v>
+        <v>43.85</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.14</v>
+        <v>47.78</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.72</v>
+        <v>46.35</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>44.49</v>
+        <v>45.1</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.04</v>
+        <v>44.65</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.4</v>
+        <v>37.91</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.44</v>
+        <v>38.97</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>56.88</v>
+        <v>57.66</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>49.37</v>
+        <v>50.05</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.05</v>
+        <v>54.79</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.27</v>
+        <v>43.87</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>51.94</v>
+        <v>52.65</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.15</v>
+        <v>43.74</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>51.91</v>
+        <v>52.62</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>60.68</v>
+        <v>61.52</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>47.41</v>
+        <v>48.06</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.08</v>
+        <v>43.68</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>49.54</v>
+        <v>50.22</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>55.45</v>
+        <v>56.22</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>84.81999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>96.59</v>
+        <v>97.92</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>67.31</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>69.28</v>
+        <v>70.23</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>56</v>
+        <v>56.77</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>58.78</v>
+        <v>59.59</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>61.85</v>
+        <v>62.7</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>63.77</v>
+        <v>64.64</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>71.66</v>
+        <v>72.64</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>72.81</v>
+        <v>73.81</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>66.11</v>
+        <v>67.02</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>80.54000000000001</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>65.79000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>64.67</v>
+        <v>65.56</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>65.12</v>
+        <v>66.02</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2602,10 +2602,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>70.27</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>71.7</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>63.57</v>
+        <v>64.45</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>65.84</v>
+        <v>66.75</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>69.91</v>
+        <v>70.87</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>70.12</v>
+        <v>71.08</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>72.76000000000001</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>72.09</v>
+        <v>73.08</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>70.95</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>63.95</v>
+        <v>64.83</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>68.92</v>
+        <v>69.87</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>58.91</v>
+        <v>59.72</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>62.21</v>
+        <v>63.06</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>53.47</v>
+        <v>54.2</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>57.44</v>
+        <v>58.23</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>65.06999999999999</v>
+        <v>65.97</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>73.23</v>
+        <v>74.23</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>51.83</v>
+        <v>52.55</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>51.81</v>
+        <v>52.52</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>47.99</v>
+        <v>48.65</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>60.27</v>
+        <v>61.1</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>59.42</v>
+        <v>60.23</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>61.37</v>
+        <v>62.21</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>62.32</v>
+        <v>63.17</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>51.55</v>
+        <v>52.26</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>52.77</v>
+        <v>53.5</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>49.88</v>
+        <v>50.57</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>55.99</v>
+        <v>56.76</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>58.84</v>
+        <v>59.65</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>60.08</v>
+        <v>60.91</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.07</v>
+        <v>46.7</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>50.78</v>
+        <v>51.48</v>
       </c>
       <c r="F112" s="7" t="inlineStr"/>
     </row>
@@ -3006,10 +3006,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>49.41</v>
+        <v>50.09</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>56.95</v>
+        <v>57.73</v>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
     </row>
@@ -3026,10 +3026,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.12</v>
+        <v>51.83</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>54.72</v>
+        <v>55.48</v>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
     </row>
@@ -3046,10 +3046,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>47.37</v>
+        <v>48.03</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>44.66</v>
+        <v>45.27</v>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.17</v>
+        <v>54.91</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.22</v>
+        <v>50.91</v>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
     </row>
@@ -3086,10 +3086,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>61.34</v>
+        <v>62.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>60.18</v>
+        <v>61</v>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
     </row>
@@ -3106,10 +3106,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>47.51</v>
+        <v>48.17</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
     </row>
@@ -3126,10 +3126,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>57.58</v>
+        <v>58.37</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>55.63</v>
+        <v>56.4</v>
       </c>
       <c r="F119" s="7" t="inlineStr"/>
     </row>
@@ -3146,10 +3146,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>53.8</v>
+        <v>54.54</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.08</v>
+        <v>54.83</v>
       </c>
       <c r="F120" s="7" t="inlineStr"/>
     </row>
@@ -3166,10 +3166,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>54.85</v>
+        <v>55.6</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>51.78</v>
+        <v>52.49</v>
       </c>
       <c r="F121" s="7" t="inlineStr"/>
     </row>
@@ -3186,10 +3186,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.1</v>
+        <v>38.63</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
       <c r="F122" s="7" t="inlineStr"/>
     </row>
@@ -3206,10 +3206,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.32</v>
+        <v>43.91</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>50.61</v>
+        <v>51.31</v>
       </c>
       <c r="F123" s="7" t="inlineStr"/>
     </row>
@@ -3226,10 +3226,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>46.82</v>
+        <v>47.46</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>52.46</v>
+        <v>53.18</v>
       </c>
       <c r="F124" s="7" t="inlineStr"/>
     </row>
@@ -3246,10 +3246,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>42.72</v>
+        <v>43.31</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.28</v>
+        <v>51.99</v>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
     </row>
@@ -3266,10 +3266,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>61.57</v>
+        <v>62.42</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>65.27</v>
+        <v>66.16</v>
       </c>
       <c r="F126" s="7" t="inlineStr"/>
     </row>
@@ -3286,10 +3286,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>79.13</v>
+        <v>80.22</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.63</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F127" s="7" t="inlineStr"/>
     </row>
@@ -3306,10 +3306,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>111.74</v>
+        <v>113.28</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>114.61</v>
+        <v>116.18</v>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
     </row>
@@ -3326,10 +3326,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>128.08</v>
+        <v>129.84</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>129.51</v>
+        <v>131.29</v>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
     </row>
@@ -3346,10 +3346,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>150.35</v>
+        <v>152.41</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>152.44</v>
+        <v>154.54</v>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
     </row>
@@ -3366,10 +3366,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>221.1</v>
+        <v>224.14</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>218.87</v>
+        <v>221.88</v>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
     </row>
@@ -3386,10 +3386,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>337.03</v>
+        <v>341.67</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>342.17</v>
+        <v>346.88</v>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
     </row>
@@ -3406,10 +3406,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>315.84</v>
+        <v>320.19</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>315.62</v>
+        <v>319.96</v>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
     </row>
@@ -3426,10 +3426,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>60.52</v>
+        <v>61.35</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>133.04</v>
+        <v>134.87</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>90.09999999999999</v>
+        <v>91.34</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>128.83</v>
+        <v>130.6</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>57.81</v>
+        <v>58.6</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>77.20999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>60.97</v>
+        <v>61.81</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>69.67</v>
+        <v>70.63</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>43.79</v>
+        <v>44.39</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>55.57</v>
+        <v>56.33</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>49.45</v>
+        <v>50.13</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>69.31</v>
+        <v>70.27</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.24</v>
+        <v>54.99</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>61.22</v>
+        <v>62.06</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>112.93</v>
+        <v>114.48</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>119.8</v>
+        <v>121.45</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>123.58</v>
+        <v>125.28</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>136.21</v>
+        <v>138.08</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>148.8</v>
+        <v>150.85</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>153.78</v>
+        <v>155.9</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>171.49</v>
+        <v>173.85</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>168.46</v>
+        <v>170.78</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>140.94</v>
+        <v>142.88</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>154.89</v>
+        <v>157.02</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>135.5</v>
+        <v>137.36</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>143.24</v>
+        <v>145.21</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>164.26</v>
+        <v>166.52</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>126.33</v>
+        <v>128.07</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>144.18</v>
+        <v>146.16</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>95.43000000000001</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>106.42</v>
+        <v>107.88</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>97.78</v>
+        <v>99.12</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>121.41</v>
+        <v>123.08</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>136.34</v>
+        <v>138.21</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>117.18</v>
+        <v>118.8</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>137.62</v>
+        <v>139.51</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>127.32</v>
+        <v>129.07</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>122.87</v>
+        <v>124.56</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>114.67</v>
+        <v>116.25</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>114.78</v>
+        <v>116.35</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>107.13</v>
+        <v>108.6</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>110.34</v>
+        <v>111.86</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>103.4</v>
+        <v>104.83</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>102.65</v>
+        <v>104.06</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>97.97</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>101.94</v>
+        <v>103.34</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>94.06</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>103.6</v>
+        <v>105.03</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>57.24</v>
+        <v>58.03</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>31.9</v>
+        <v>32.34</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.35</v>
+        <v>40.9</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>77.45</v>
+        <v>78.52</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>96.06</v>
+        <v>97.38</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>121.16</v>
+        <v>122.83</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>129.99</v>
+        <v>131.78</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>108.56</v>
+        <v>110.05</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>112.29</v>
+        <v>113.83</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>91.31999999999999</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>90.12</v>
+        <v>91.36</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>187.27</v>
+        <v>189.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>207.49</v>
+        <v>210.34</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>170.66</v>
+        <v>173.01</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>169.27</v>
+        <v>171.6</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>156.29</v>
+        <v>158.44</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>146.35</v>
+        <v>148.36</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>132.33</v>
+        <v>134.15</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.11</v>
+        <v>140.01</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>116.72</v>
+        <v>118.33</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>129.06</v>
+        <v>130.83</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>121.84</v>
+        <v>123.52</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>137.82</v>
+        <v>139.71</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>93.94</v>
+        <v>95.23</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>112.8</v>
+        <v>114.35</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>87.83</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>102.59</v>
+        <v>104</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>72.12</v>
+        <v>73.11</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>80.08</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>134.47</v>
+        <v>136.32</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>133.47</v>
+        <v>135.31</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>85.09</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>96.64</v>
+        <v>97.97</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>64.87</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>62.44</v>
+        <v>63.3</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>61.89</v>
+        <v>62.74</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>48.49</v>
+        <v>49.15</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.24</v>
+        <v>48.9</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.28</v>
+        <v>46.92</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>43.99</v>
+        <v>44.6</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.13</v>
+        <v>29.53</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.51</v>
+        <v>30.93</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>43.62</v>
+        <v>44.22</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>51.68</v>
+        <v>52.39</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>45.98</v>
+        <v>46.61</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>49.78</v>
+        <v>50.47</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>71.11</v>
+        <v>72.09</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>70.97</v>
+        <v>71.95</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>46.66</v>
+        <v>47.3</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>48.74</v>
+        <v>49.41</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>52.47</v>
+        <v>53.19</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>73.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71</v>
+        <v>71.98</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>45.43</v>
+        <v>46.05</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>53.6</v>
+        <v>54.34</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>46.51</v>
+        <v>47.15</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>49.4</v>
+        <v>50.08</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.35</v>
+        <v>45.98</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>37.72</v>
+        <v>38.24</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.2</v>
+        <v>39.74</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>30.97</v>
+        <v>31.4</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.4</v>
+        <v>35.89</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>54.89</v>
+        <v>55.64</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>83.79000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>94.73999999999999</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.28</v>
+        <v>46.91</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>25.96</v>
+        <v>26.32</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>30.78</v>
+        <v>31.21</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>19.93</v>
+        <v>20.2</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>26.72</v>
+        <v>27.08</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.73</v>
+        <v>11.9</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>37.99</v>
+        <v>38.51</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.15</v>
+        <v>40.7</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>59.37</v>
+        <v>60.19</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>60.46</v>
+        <v>61.29</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>79.05</v>
+        <v>80.14</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>84.78</v>
+        <v>85.95</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>91.73</v>
+        <v>93</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>87.23999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>91.86</v>
+        <v>93.12</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>163.72</v>
+        <v>165.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>191.22</v>
+        <v>193.85</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>250.22</v>
+        <v>253.66</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>278.76</v>
+        <v>282.59</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>328.43</v>
+        <v>332.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>438.08</v>
+        <v>444.11</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>367.51</v>
+        <v>372.56</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>416.98</v>
+        <v>422.72</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>169.17</v>
+        <v>171.49</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>192</v>
+        <v>194.64</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>149.29</v>
+        <v>151.34</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>169.58</v>
+        <v>171.91</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>136.37</v>
+        <v>138.24</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>141.68</v>
+        <v>143.63</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>112.19</v>
+        <v>113.73</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>127.55</v>
+        <v>129.3</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>84.31999999999999</v>
+        <v>85.48</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>95.48</v>
+        <v>96.8</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>89.17</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>89.22</v>
+        <v>90.45</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>83.89</v>
+        <v>85.05</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>74.23</v>
+        <v>75.25</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>76.08</v>
+        <v>77.13</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>77.08</v>
+        <v>78.14</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>91.17</v>
+        <v>92.42</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>93.75</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.09</v>
+        <v>41.66</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.53</v>
+        <v>57.31</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.09</v>
+        <v>25.44</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.21</v>
+        <v>35.69</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.36</v>
+        <v>40.92</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>40.66</v>
+        <v>41.22</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.52</v>
+        <v>28.92</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.57</v>
+        <v>26.94</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.13</v>
+        <v>40.69</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.39</v>
+        <v>38.91</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>63.78</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.13</v>
+        <v>61.97</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>55.28</v>
+        <v>56.04</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.05</v>
+        <v>52.77</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.03</v>
+        <v>53.75</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>52.42</v>
+        <v>53.14</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>86.34</v>
+        <v>87.53</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>116.22</v>
+        <v>117.82</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>73.23</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>70.98</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>76.86</v>
+        <v>77.91</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>147.26</v>
+        <v>149.28</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>152.07</v>
+        <v>154.16</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>185.48</v>
+        <v>188.03</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>221.57</v>
+        <v>224.61</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>187.95</v>
+        <v>190.54</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>224.21</v>
+        <v>227.3</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>133.71</v>
+        <v>135.55</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>162.34</v>
+        <v>164.57</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.37</v>
+        <v>23.69</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.45</v>
+        <v>32.89</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>51.67</v>
+        <v>52.38</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>54.5</v>
+        <v>55.25</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>99.40000000000001</v>
+        <v>100.77</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>100.15</v>
+        <v>101.52</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>78.87</v>
+        <v>79.95</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>70.95999999999999</v>
+        <v>71.94</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>117.39</v>
+        <v>119</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>112.69</v>
+        <v>114.24</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>125.33</v>
+        <v>127.06</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>128.75</v>
+        <v>130.52</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>102.72</v>
+        <v>104.14</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>103.53</v>
+        <v>104.96</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>102.97</v>
+        <v>104.39</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>100.97</v>
+        <v>102.36</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>105.64</v>
+        <v>107.09</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>115.83</v>
+        <v>117.43</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>223.55</v>
+        <v>226.63</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>334.29</v>
+        <v>338.89</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>119.59</v>
+        <v>121.23</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>132.37</v>
+        <v>134.19</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>126.51</v>
+        <v>128.25</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>134.94</v>
+        <v>136.79</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.45</v>
+        <v>36.96</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.65</v>
+        <v>24.99</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>26.99</v>
+        <v>27.36</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>40.59</v>
+        <v>41.15</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.41</v>
+        <v>34.88</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>59.34</v>
+        <v>60.16</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>55.6</v>
+        <v>56.36</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>100.93</v>
+        <v>101.85</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>114.88</v>
+        <v>115.93</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.28</v>
+        <v>90.69</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.56</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5812,6 +5812,26 @@
         <v>85.3</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="F254" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5824,7 +5844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5874,10 +5894,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>537.86</v>
+        <v>545.26</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>687.21</v>
+        <v>696.66</v>
       </c>
     </row>
     <row r="3">
@@ -5893,10 +5913,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>137.54</v>
+        <v>139.44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
     </row>
     <row r="4">
@@ -5912,10 +5932,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>195.86</v>
+        <v>198.56</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>201.27</v>
+        <v>204.04</v>
       </c>
     </row>
     <row r="5">
@@ -5931,10 +5951,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>186.29</v>
+        <v>188.85</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>245.14</v>
+        <v>248.52</v>
       </c>
     </row>
     <row r="6">
@@ -5950,10 +5970,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>120.12</v>
+        <v>121.77</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>135.2</v>
+        <v>137.06</v>
       </c>
     </row>
     <row r="7">
@@ -5969,10 +5989,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>142.44</v>
+        <v>144.4</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>176.81</v>
+        <v>179.25</v>
       </c>
     </row>
     <row r="8">
@@ -5988,10 +6008,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>99.48999999999999</v>
+        <v>100.86</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102.3</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="9">
@@ -6007,10 +6027,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>73.78</v>
+        <v>74.8</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -6026,10 +6046,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>63.4</v>
+        <v>64.27</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>69.36</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6045,10 +6065,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55.58</v>
+        <v>56.34</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>61.27</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="12">
@@ -6064,10 +6084,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>48.52</v>
+        <v>49.19</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>55.61</v>
+        <v>56.37</v>
       </c>
     </row>
     <row r="13">
@@ -6083,10 +6103,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>56.69</v>
+        <v>57.47</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>57.51</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="14">
@@ -6102,10 +6122,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.07</v>
+        <v>57.86</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>80.44</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="15">
@@ -6121,10 +6141,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>69.61</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>88.61</v>
       </c>
     </row>
     <row r="16">
@@ -6140,10 +6160,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>80.89</v>
+        <v>82</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>115.38</v>
+        <v>116.97</v>
       </c>
     </row>
     <row r="17">
@@ -6159,10 +6179,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>58.8</v>
+        <v>59.61</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>66.59</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -6178,10 +6198,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.76</v>
+        <v>64.64</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>69.23</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -6197,10 +6217,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.08</v>
+        <v>57.87</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>61.42</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="20">
@@ -6216,10 +6236,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -6235,10 +6255,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>68.56</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="22">
@@ -6254,10 +6274,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>73.91</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>78.84</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="23">
@@ -6273,10 +6293,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>88.31999999999999</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>112.76</v>
+        <v>114.31</v>
       </c>
     </row>
     <row r="24">
@@ -6292,10 +6312,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>84.63</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
@@ -6311,10 +6331,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>121.37</v>
+        <v>123.04</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>136.5</v>
+        <v>138.37</v>
       </c>
     </row>
     <row r="26">
@@ -6330,10 +6350,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>109.73</v>
+        <v>111.24</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>119.6</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="27">
@@ -6349,10 +6369,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>128.18</v>
+        <v>129.94</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>131.67</v>
+        <v>133.48</v>
       </c>
     </row>
     <row r="28">
@@ -6368,10 +6388,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>163.45</v>
+        <v>165.7</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>189.83</v>
+        <v>192.44</v>
       </c>
     </row>
     <row r="29">
@@ -6387,10 +6407,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>80.05</v>
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -6406,10 +6426,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>77.29000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>82.29000000000001</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="31">
@@ -6425,10 +6445,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>55.5</v>
+        <v>56.26</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="32">
@@ -6444,10 +6464,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>80.37</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="33">
@@ -6463,10 +6483,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>98.13</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="34">
@@ -6482,10 +6502,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>76.38</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>95.31</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="35">
@@ -6501,10 +6521,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>90.70999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>108.85</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="36">
@@ -6520,10 +6540,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>89.84</v>
+        <v>91.08</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>110.03</v>
+        <v>111.54</v>
       </c>
     </row>
     <row r="37">
@@ -6539,10 +6559,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>87.44</v>
+        <v>88.64</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>101.62</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="38">
@@ -6558,10 +6578,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>107.31</v>
+        <v>108.79</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>110.45</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="39">
@@ -6577,10 +6597,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>88.23</v>
+        <v>89.44</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>99.75</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="40">
@@ -6596,10 +6616,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.68</v>
+        <v>48.34</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>47.52</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="41">
@@ -6615,10 +6635,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>85.98</v>
+        <v>87.17</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>95.34</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -6634,10 +6654,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>68.48</v>
+        <v>69.42</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>83.38</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="43">
@@ -6653,10 +6673,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>71.64</v>
+        <v>72.63</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>87.87</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="44">
@@ -6672,10 +6692,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>79.19</v>
+        <v>80.28</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>95.76000000000001</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="45">
@@ -6691,10 +6711,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>51.46</v>
+        <v>52.17</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>59.89</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="46">
@@ -6710,10 +6730,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>123.29</v>
+        <v>124.99</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>186.98</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="47">
@@ -6729,10 +6749,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.06</v>
+        <v>61.9</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>99.86</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="48">
@@ -6748,10 +6768,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>56.98</v>
+        <v>57.76</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>68.3</v>
+        <v>69.23999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -6767,10 +6787,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>108.07</v>
+        <v>109.56</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>98.59</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="50">
@@ -6786,10 +6806,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>72.92</v>
+        <v>73.92</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>77.94</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="51">
@@ -6805,10 +6825,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>270.11</v>
+        <v>273.83</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>453.84</v>
+        <v>460.08</v>
       </c>
     </row>
     <row r="52">
@@ -6824,10 +6844,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.11</v>
+        <v>40.66</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.08</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="53">
@@ -6843,10 +6863,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>32.88</v>
+        <v>33.33</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.29</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="54">
@@ -6862,10 +6882,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.13</v>
+        <v>33.59</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.35</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="55">
@@ -6881,10 +6901,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>39.62</v>
+        <v>40.16</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.32</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="56">
@@ -6900,10 +6920,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>51.7</v>
+        <v>52.41</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>58.46</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="57">
@@ -6919,10 +6939,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="58">
@@ -6938,10 +6958,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>44.62</v>
+        <v>45.24</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>49.65</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="59">
@@ -6957,10 +6977,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.47</v>
+        <v>36.97</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.37</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="60">
@@ -6976,10 +6996,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>39.75</v>
+        <v>40.3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="61">
@@ -6995,10 +7015,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>36.98</v>
+        <v>37.49</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>39.67</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="62">
@@ -7014,10 +7034,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>86.09</v>
+        <v>87.27</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>61.25</v>
+        <v>62.09</v>
       </c>
     </row>
     <row r="63">
@@ -7033,10 +7053,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>46.59</v>
+        <v>47.23</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="64">
@@ -7052,10 +7072,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>45.44</v>
+        <v>46.06</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.14</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="65">
@@ -7071,10 +7091,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>97.26000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>41.68</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="66">
@@ -7090,10 +7110,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.08</v>
+        <v>31.51</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>35.85</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="67">
@@ -7109,10 +7129,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.13</v>
+        <v>27.5</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>27.75</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="68">
@@ -7128,10 +7148,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>40.47</v>
+        <v>41.03</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>57.47</v>
+        <v>58.26</v>
       </c>
     </row>
     <row r="69">
@@ -7147,10 +7167,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>24.91</v>
+        <v>25.25</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.55</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="70">
@@ -7166,10 +7186,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>38.51</v>
+        <v>39.04</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.08</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="71">
@@ -7185,10 +7205,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.4</v>
+        <v>42.98</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>46.47</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="72">
@@ -7204,10 +7224,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>37.94</v>
+        <v>38.46</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>39.98</v>
+        <v>40.53</v>
       </c>
     </row>
     <row r="73">
@@ -7223,10 +7243,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.24</v>
+        <v>39.78</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>40.69</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="74">
@@ -7242,10 +7262,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>56.45</v>
+        <v>57.23</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>59.46</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="75">
@@ -7261,10 +7281,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>42.44</v>
+        <v>43.02</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.02</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="76">
@@ -7280,10 +7300,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.34</v>
+        <v>47.99</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>71.34999999999999</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="77">
@@ -7299,10 +7319,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.37</v>
+        <v>39.91</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.29</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="78">
@@ -7318,10 +7338,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.2</v>
+        <v>38.72</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.26</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="79">
@@ -7337,10 +7357,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.14</v>
+        <v>47.78</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.72</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="80">
@@ -7356,10 +7376,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>44.49</v>
+        <v>45.1</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.04</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="81">
@@ -7375,10 +7395,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.4</v>
+        <v>37.91</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.44</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="82">
@@ -7394,10 +7414,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>56.88</v>
+        <v>57.66</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>49.37</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="83">
@@ -7413,10 +7433,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.05</v>
+        <v>54.79</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.27</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="84">
@@ -7432,10 +7452,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>51.94</v>
+        <v>52.65</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.15</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="85">
@@ -7451,10 +7471,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>51.91</v>
+        <v>52.62</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>60.68</v>
+        <v>61.52</v>
       </c>
     </row>
     <row r="86">
@@ -7470,10 +7490,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>47.41</v>
+        <v>48.06</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.08</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="87">
@@ -7489,10 +7509,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>49.54</v>
+        <v>50.22</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>55.45</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="88">
@@ -7508,10 +7528,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>84.81999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>96.59</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="89">
@@ -7527,10 +7547,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>67.31</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>69.28</v>
+        <v>70.23</v>
       </c>
     </row>
     <row r="90">
@@ -7546,10 +7566,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>56</v>
+        <v>56.77</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>58.78</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="91">
@@ -7565,10 +7585,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>61.85</v>
+        <v>62.7</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>63.77</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="92">
@@ -7584,10 +7604,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>71.66</v>
+        <v>72.64</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>72.81</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="93">
@@ -7603,10 +7623,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>66.11</v>
+        <v>67.02</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -7622,10 +7642,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>65.79000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="95">
@@ -7641,10 +7661,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>64.67</v>
+        <v>65.56</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>65.12</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="96">
@@ -7660,10 +7680,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>70.27</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>71.7</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -7679,10 +7699,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>63.57</v>
+        <v>64.45</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>65.84</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="98">
@@ -7698,10 +7718,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>69.91</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="99">
@@ -7717,10 +7737,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>70.12</v>
+        <v>71.08</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>73.76000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -7736,10 +7756,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>72.09</v>
+        <v>73.08</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>70.95</v>
+        <v>71.93000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7755,10 +7775,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>63.95</v>
+        <v>64.83</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>68.92</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="102">
@@ -7774,10 +7794,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>58.91</v>
+        <v>59.72</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>62.21</v>
+        <v>63.06</v>
       </c>
     </row>
     <row r="103">
@@ -7793,10 +7813,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>53.47</v>
+        <v>54.2</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>57.44</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="104">
@@ -7812,10 +7832,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>65.06999999999999</v>
+        <v>65.97</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>73.23</v>
+        <v>74.23</v>
       </c>
     </row>
     <row r="105">
@@ -7831,10 +7851,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>51.83</v>
+        <v>52.55</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>51.81</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="106">
@@ -7850,10 +7870,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>47.99</v>
+        <v>48.65</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="107">
@@ -7869,10 +7889,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>60.27</v>
+        <v>61.1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>59.42</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="108">
@@ -7888,10 +7908,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>61.37</v>
+        <v>62.21</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>62.32</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="109">
@@ -7907,10 +7927,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>51.55</v>
+        <v>52.26</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>52.77</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="110">
@@ -7926,10 +7946,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>49.88</v>
+        <v>50.57</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>55.99</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="111">
@@ -7945,10 +7965,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>58.84</v>
+        <v>59.65</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>60.08</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="112">
@@ -7964,10 +7984,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.07</v>
+        <v>46.7</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>50.78</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="113">
@@ -7983,10 +8003,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>49.41</v>
+        <v>50.09</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>56.95</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="114">
@@ -8002,10 +8022,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.12</v>
+        <v>51.83</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>54.72</v>
+        <v>55.48</v>
       </c>
     </row>
     <row r="115">
@@ -8021,10 +8041,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>47.37</v>
+        <v>48.03</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>44.66</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="116">
@@ -8040,10 +8060,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.17</v>
+        <v>54.91</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.22</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="117">
@@ -8059,10 +8079,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>61.34</v>
+        <v>62.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>60.18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118">
@@ -8078,10 +8098,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>47.51</v>
+        <v>48.17</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="119">
@@ -8097,10 +8117,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>57.58</v>
+        <v>58.37</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>55.63</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="120">
@@ -8116,10 +8136,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>53.8</v>
+        <v>54.54</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.08</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="121">
@@ -8135,10 +8155,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>54.85</v>
+        <v>55.6</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>51.78</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="122">
@@ -8154,10 +8174,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.1</v>
+        <v>38.63</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="123">
@@ -8173,10 +8193,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.32</v>
+        <v>43.91</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>50.61</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="124">
@@ -8192,10 +8212,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>46.82</v>
+        <v>47.46</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>52.46</v>
+        <v>53.18</v>
       </c>
     </row>
     <row r="125">
@@ -8211,10 +8231,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>42.72</v>
+        <v>43.31</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.28</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="126">
@@ -8230,10 +8250,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>61.57</v>
+        <v>62.42</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>65.27</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="127">
@@ -8249,10 +8269,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>79.13</v>
+        <v>80.22</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.63</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8268,10 +8288,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>111.74</v>
+        <v>113.28</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>114.61</v>
+        <v>116.18</v>
       </c>
     </row>
     <row r="129">
@@ -8287,10 +8307,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>128.08</v>
+        <v>129.84</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>129.51</v>
+        <v>131.29</v>
       </c>
     </row>
     <row r="130">
@@ -8306,10 +8326,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>150.35</v>
+        <v>152.41</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>152.44</v>
+        <v>154.54</v>
       </c>
     </row>
     <row r="131">
@@ -8325,10 +8345,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>221.1</v>
+        <v>224.14</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>218.87</v>
+        <v>221.88</v>
       </c>
     </row>
     <row r="132">
@@ -8344,10 +8364,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>337.03</v>
+        <v>341.67</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>342.17</v>
+        <v>346.88</v>
       </c>
     </row>
     <row r="133">
@@ -8363,10 +8383,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>315.84</v>
+        <v>320.19</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>315.62</v>
+        <v>319.96</v>
       </c>
     </row>
     <row r="134">
@@ -8382,10 +8402,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>60.52</v>
+        <v>61.35</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -8401,10 +8421,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>133.04</v>
+        <v>134.87</v>
       </c>
     </row>
     <row r="136">
@@ -8420,10 +8440,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>90.09999999999999</v>
+        <v>91.34</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>128.83</v>
+        <v>130.6</v>
       </c>
     </row>
     <row r="137">
@@ -8439,10 +8459,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>57.81</v>
+        <v>58.6</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>77.20999999999999</v>
+        <v>78.27</v>
       </c>
     </row>
     <row r="138">
@@ -8458,10 +8478,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>60.97</v>
+        <v>61.81</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>69.67</v>
+        <v>70.63</v>
       </c>
     </row>
     <row r="139">
@@ -8477,10 +8497,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>43.79</v>
+        <v>44.39</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>55.57</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="140">
@@ -8496,10 +8516,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>49.45</v>
+        <v>50.13</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>69.31</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="141">
@@ -8515,10 +8535,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.24</v>
+        <v>54.99</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>61.22</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="142">
@@ -8534,10 +8554,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>112.93</v>
+        <v>114.48</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>119.8</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="143">
@@ -8553,10 +8573,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>123.58</v>
+        <v>125.28</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>136.21</v>
+        <v>138.08</v>
       </c>
     </row>
     <row r="144">
@@ -8572,10 +8592,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>148.8</v>
+        <v>150.85</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>153.78</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="145">
@@ -8591,10 +8611,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>171.49</v>
+        <v>173.85</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>168.46</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="146">
@@ -8610,10 +8630,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>140.94</v>
+        <v>142.88</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>154.89</v>
+        <v>157.02</v>
       </c>
     </row>
     <row r="147">
@@ -8629,10 +8649,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>135.5</v>
+        <v>137.36</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>143.24</v>
+        <v>145.21</v>
       </c>
     </row>
     <row r="148">
@@ -8648,10 +8668,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>164.26</v>
+        <v>166.52</v>
       </c>
     </row>
     <row r="149">
@@ -8667,10 +8687,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>126.33</v>
+        <v>128.07</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>144.18</v>
+        <v>146.16</v>
       </c>
     </row>
     <row r="150">
@@ -8686,10 +8706,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>95.43000000000001</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>106.42</v>
+        <v>107.88</v>
       </c>
     </row>
     <row r="151">
@@ -8705,10 +8725,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>97.78</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="152">
@@ -8724,10 +8744,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>121.41</v>
+        <v>123.08</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>136.34</v>
+        <v>138.21</v>
       </c>
     </row>
     <row r="153">
@@ -8743,10 +8763,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>117.18</v>
+        <v>118.8</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>137.62</v>
+        <v>139.51</v>
       </c>
     </row>
     <row r="154">
@@ -8762,10 +8782,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>127.32</v>
+        <v>129.07</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>122.87</v>
+        <v>124.56</v>
       </c>
     </row>
     <row r="155">
@@ -8781,10 +8801,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>114.67</v>
+        <v>116.25</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>114.78</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="156">
@@ -8800,10 +8820,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>107.13</v>
+        <v>108.6</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>110.34</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="157">
@@ -8819,10 +8839,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>103.4</v>
+        <v>104.83</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>102.65</v>
+        <v>104.06</v>
       </c>
     </row>
     <row r="158">
@@ -8838,10 +8858,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>97.97</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>101.94</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="159">
@@ -8857,10 +8877,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>94.06</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>103.6</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="160">
@@ -8876,10 +8896,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>57.24</v>
+        <v>58.03</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="161">
@@ -8895,10 +8915,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>31.9</v>
+        <v>32.34</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.35</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="162">
@@ -8914,10 +8934,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>77.45</v>
+        <v>78.52</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>96.06</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="163">
@@ -8933,10 +8953,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>121.16</v>
+        <v>122.83</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>129.99</v>
+        <v>131.78</v>
       </c>
     </row>
     <row r="164">
@@ -8952,10 +8972,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>108.56</v>
+        <v>110.05</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>112.29</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="165">
@@ -8971,10 +8991,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>91.31999999999999</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>90.12</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="166">
@@ -8990,10 +9010,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>187.27</v>
+        <v>189.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>207.49</v>
+        <v>210.34</v>
       </c>
     </row>
     <row r="167">
@@ -9009,10 +9029,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>170.66</v>
+        <v>173.01</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>169.27</v>
+        <v>171.6</v>
       </c>
     </row>
     <row r="168">
@@ -9028,10 +9048,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>156.29</v>
+        <v>158.44</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>146.35</v>
+        <v>148.36</v>
       </c>
     </row>
     <row r="169">
@@ -9047,10 +9067,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>132.33</v>
+        <v>134.15</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.11</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="170">
@@ -9066,10 +9086,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>116.72</v>
+        <v>118.33</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>129.06</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="171">
@@ -9085,10 +9105,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>121.84</v>
+        <v>123.52</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>137.82</v>
+        <v>139.71</v>
       </c>
     </row>
     <row r="172">
@@ -9104,10 +9124,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>93.94</v>
+        <v>95.23</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>112.8</v>
+        <v>114.35</v>
       </c>
     </row>
     <row r="173">
@@ -9123,10 +9143,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>87.83</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>102.59</v>
+        <v>104</v>
       </c>
     </row>
     <row r="174">
@@ -9142,10 +9162,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>72.12</v>
+        <v>73.11</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>80.08</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9161,10 +9181,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>134.47</v>
+        <v>136.32</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>133.47</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="176">
@@ -9180,10 +9200,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>85.09</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>96.64</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="177">
@@ -9199,10 +9219,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>64.87</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>62.44</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="178">
@@ -9218,10 +9238,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>61.89</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="179">
@@ -9237,10 +9257,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>48.49</v>
+        <v>49.15</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.24</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="180">
@@ -9256,10 +9276,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.28</v>
+        <v>46.92</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>43.99</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="181">
@@ -9275,10 +9295,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.13</v>
+        <v>29.53</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.51</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="182">
@@ -9294,10 +9314,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>43.62</v>
+        <v>44.22</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>51.68</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="183">
@@ -9313,10 +9333,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>45.98</v>
+        <v>46.61</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>49.78</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="184">
@@ -9332,10 +9352,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>71.11</v>
+        <v>72.09</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="185">
@@ -9351,10 +9371,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>70.97</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="186">
@@ -9370,10 +9390,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>46.66</v>
+        <v>47.3</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>48.74</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="187">
@@ -9389,10 +9409,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>52.47</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="188">
@@ -9408,10 +9428,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>73.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="189">
@@ -9427,10 +9447,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>45.43</v>
+        <v>46.05</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>53.6</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="190">
@@ -9446,10 +9466,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>46.51</v>
+        <v>47.15</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>49.4</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="191">
@@ -9465,10 +9485,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.35</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="192">
@@ -9484,10 +9504,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>37.72</v>
+        <v>38.24</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.2</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="193">
@@ -9503,10 +9523,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>30.97</v>
+        <v>31.4</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.4</v>
+        <v>35.89</v>
       </c>
     </row>
     <row r="194">
@@ -9522,10 +9542,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>54.89</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="195">
@@ -9541,10 +9561,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>83.79000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>94.73999999999999</v>
+        <v>96.04000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -9560,10 +9580,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.28</v>
+        <v>46.91</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="197">
@@ -9579,10 +9599,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>25.96</v>
+        <v>26.32</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>30.78</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="198">
@@ -9598,10 +9618,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>19.93</v>
+        <v>20.2</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>26.72</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="199">
@@ -9617,10 +9637,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.73</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="200">
@@ -9636,10 +9656,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>37.99</v>
+        <v>38.51</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.15</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="201">
@@ -9655,10 +9675,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>59.37</v>
+        <v>60.19</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>60.46</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="202">
@@ -9674,10 +9694,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>79.05</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="203">
@@ -9693,10 +9713,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>84.78</v>
+        <v>85.95</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>91.73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="204">
@@ -9712,10 +9732,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>87.23999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>91.86</v>
+        <v>93.12</v>
       </c>
     </row>
     <row r="205">
@@ -9731,10 +9751,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>163.72</v>
+        <v>165.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>191.22</v>
+        <v>193.85</v>
       </c>
     </row>
     <row r="206">
@@ -9750,10 +9770,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>250.22</v>
+        <v>253.66</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>278.76</v>
+        <v>282.59</v>
       </c>
     </row>
     <row r="207">
@@ -9769,10 +9789,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>328.43</v>
+        <v>332.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>438.08</v>
+        <v>444.11</v>
       </c>
     </row>
     <row r="208">
@@ -9788,10 +9808,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>367.51</v>
+        <v>372.56</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>416.98</v>
+        <v>422.72</v>
       </c>
     </row>
     <row r="209">
@@ -9807,10 +9827,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>169.17</v>
+        <v>171.49</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>192</v>
+        <v>194.64</v>
       </c>
     </row>
     <row r="210">
@@ -9826,10 +9846,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>149.29</v>
+        <v>151.34</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>169.58</v>
+        <v>171.91</v>
       </c>
     </row>
     <row r="211">
@@ -9845,10 +9865,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>136.37</v>
+        <v>138.24</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>141.68</v>
+        <v>143.63</v>
       </c>
     </row>
     <row r="212">
@@ -9864,10 +9884,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>112.19</v>
+        <v>113.73</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>127.55</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="213">
@@ -9883,10 +9903,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>84.31999999999999</v>
+        <v>85.48</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>75.43000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -9902,10 +9922,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>95.48</v>
+        <v>96.8</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>89.17</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -9921,10 +9941,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>89.22</v>
+        <v>90.45</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>83.89</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="216">
@@ -9940,10 +9960,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>74.23</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="217">
@@ -9959,10 +9979,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>76.08</v>
+        <v>77.13</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>77.08</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="218">
@@ -9978,10 +9998,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>91.17</v>
+        <v>92.42</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>93.75</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -9997,10 +10017,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.09</v>
+        <v>41.66</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.53</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="220">
@@ -10016,10 +10036,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.09</v>
+        <v>25.44</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.21</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="221">
@@ -10035,10 +10055,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.36</v>
+        <v>40.92</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>40.66</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="222">
@@ -10054,10 +10074,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.52</v>
+        <v>28.92</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.57</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="223">
@@ -10073,10 +10093,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.13</v>
+        <v>40.69</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.39</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="224">
@@ -10092,10 +10112,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>63.78</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.13</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="225">
@@ -10111,10 +10131,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>55.28</v>
+        <v>56.04</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.05</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="226">
@@ -10130,10 +10150,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.03</v>
+        <v>53.75</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>52.42</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="227">
@@ -10149,10 +10169,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>86.34</v>
+        <v>87.53</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>116.22</v>
+        <v>117.82</v>
       </c>
     </row>
     <row r="228">
@@ -10168,10 +10188,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>73.23</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>70.98</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -10187,10 +10207,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>76.86</v>
+        <v>77.91</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="230">
@@ -10206,10 +10226,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>147.26</v>
+        <v>149.28</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>152.07</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="231">
@@ -10225,10 +10245,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>185.48</v>
+        <v>188.03</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>221.57</v>
+        <v>224.61</v>
       </c>
     </row>
     <row r="232">
@@ -10244,10 +10264,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>187.95</v>
+        <v>190.54</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>224.21</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="233">
@@ -10263,10 +10283,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>133.71</v>
+        <v>135.55</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>162.34</v>
+        <v>164.57</v>
       </c>
     </row>
     <row r="234">
@@ -10282,10 +10302,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.37</v>
+        <v>23.69</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.45</v>
+        <v>32.89</v>
       </c>
     </row>
     <row r="235">
@@ -10301,10 +10321,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>51.67</v>
+        <v>52.38</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>54.5</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="236">
@@ -10320,10 +10340,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>99.40000000000001</v>
+        <v>100.77</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>100.15</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="237">
@@ -10339,10 +10359,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>78.87</v>
+        <v>79.95</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>70.95999999999999</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="238">
@@ -10358,10 +10378,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>117.39</v>
+        <v>119</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>112.69</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="239">
@@ -10377,10 +10397,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>125.33</v>
+        <v>127.06</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>128.75</v>
+        <v>130.52</v>
       </c>
     </row>
     <row r="240">
@@ -10396,10 +10416,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>102.72</v>
+        <v>104.14</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>103.53</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="241">
@@ -10415,10 +10435,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>102.97</v>
+        <v>104.39</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>100.97</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="242">
@@ -10434,10 +10454,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>105.64</v>
+        <v>107.09</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>115.83</v>
+        <v>117.43</v>
       </c>
     </row>
     <row r="243">
@@ -10453,10 +10473,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>223.55</v>
+        <v>226.63</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>334.29</v>
+        <v>338.89</v>
       </c>
     </row>
     <row r="244">
@@ -10472,10 +10492,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>119.59</v>
+        <v>121.23</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>132.37</v>
+        <v>134.19</v>
       </c>
     </row>
     <row r="245">
@@ -10491,10 +10511,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>126.51</v>
+        <v>128.25</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>134.94</v>
+        <v>136.79</v>
       </c>
     </row>
     <row r="246">
@@ -10510,10 +10530,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.45</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="247">
@@ -10529,10 +10549,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.65</v>
+        <v>24.99</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>26.99</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="248">
@@ -10548,10 +10568,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>40.59</v>
+        <v>41.15</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.41</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="249">
@@ -10567,10 +10587,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>59.34</v>
+        <v>60.16</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>55.6</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="250">
@@ -10586,10 +10606,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>100.93</v>
+        <v>101.85</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>114.88</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="251">
@@ -10605,10 +10625,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.28</v>
+        <v>90.69</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.56</v>
+        <v>87.95999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10649,8 +10669,27 @@
         <v>85.3</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>93.59</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B253">
+  <conditionalFormatting sqref="B2:B254">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10662,7 +10701,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C253">
+  <conditionalFormatting sqref="C2:C254">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10674,7 +10713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D253">
+  <conditionalFormatting sqref="D2:D254">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10686,7 +10725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E253">
+  <conditionalFormatting sqref="E2:E254">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>89.01000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>101.24</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>90.47</v>
+        <v>78.12</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>103.06</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>97.48</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>108.14</v>
+        <v>102.74</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>100.76</v>
+        <v>96.2</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>111.85</v>
+        <v>105.96</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84.19</v>
+        <v>85.31</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>92.48</v>
+        <v>93.34</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>88.78</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>96.42</v>
+        <v>97.14</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>90.34999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>99.73999999999999</v>
+        <v>99.83</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>98.65000000000001</v>
+        <v>98.55</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>109.01</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.34</v>
+        <v>80.39</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.97</v>
+        <v>87.83</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.84999999999999</v>
+        <v>94.69</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.86</v>
+        <v>103.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: May 2026</t>
+          <t>Data through: Jun 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F254"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5833,6 +5833,26 @@
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="F255" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5844,7 +5864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10688,8 +10708,27 @@
         <v>93.59</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>83.26000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B254">
+  <conditionalFormatting sqref="B2:B255">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10701,7 +10740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C254">
+  <conditionalFormatting sqref="C2:C255">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10713,7 +10752,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D254">
+  <conditionalFormatting sqref="D2:D255">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10725,7 +10764,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E254">
+  <conditionalFormatting sqref="E2:E255">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>77.27</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>80.84999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>78.12</v>
+        <v>74.75</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>81.76000000000001</v>
+        <v>80.81</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>102.74</v>
+        <v>98.87</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>96.2</v>
+        <v>91.62</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>105.96</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>85.31</v>
+        <v>86.91</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>93.34</v>
+        <v>95.84</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>88.78</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>97.14</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>90.51000000000001</v>
+        <v>91.22</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>99.83</v>
+        <v>101.16</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>98.55</v>
+        <v>99.11</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>108.8</v>
+        <v>109.96</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.39</v>
+        <v>80.5</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.83</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.69</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.43</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jun 2026</t>
+          <t>Data through: Jul 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5853,6 +5853,26 @@
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="F256" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5864,7 +5884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10727,8 +10747,27 @@
         <v>83.26000000000001</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>122.76</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B255">
+  <conditionalFormatting sqref="B2:B256">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10740,7 +10779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C255">
+  <conditionalFormatting sqref="C2:C256">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10752,7 +10791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D255">
+  <conditionalFormatting sqref="D2:D256">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10764,7 +10803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E255">
+  <conditionalFormatting sqref="E2:E256">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74.18000000000001</v>
+        <v>68.78</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>74.75</v>
+        <v>69.36</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>80.81</v>
+        <v>76.09</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>89.15000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>98.87</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>91.62</v>
+        <v>88.94</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>101.6</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>86.91</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>95.84</v>
+        <v>96.92</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>90.31999999999999</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>99.56</v>
+        <v>101.09</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>91.22</v>
+        <v>91.87</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>101.16</v>
+        <v>102.01</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>99.11</v>
+        <v>100.25</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>109.96</v>
+        <v>111.35</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80.5</v>
+        <v>80.64</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>88.04000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>94.59999999999999</v>
+        <v>95.17</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103.36</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jul 2026</t>
+          <t>Data through: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>545.26</v>
+        <v>548.53</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>696.66</v>
+        <v>700.84</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>139.44</v>
+        <v>140.27</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>198.56</v>
+        <v>199.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>204.04</v>
+        <v>205.26</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>188.85</v>
+        <v>189.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>248.52</v>
+        <v>250.01</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>121.77</v>
+        <v>122.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137.06</v>
+        <v>137.89</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>144.4</v>
+        <v>145.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>179.25</v>
+        <v>180.32</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.86</v>
+        <v>101.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>103.71</v>
+        <v>104.33</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>74.8</v>
+        <v>75.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>82.59</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>64.27</v>
+        <v>64.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>70.31999999999999</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56.34</v>
+        <v>56.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.11</v>
+        <v>62.48</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>49.19</v>
+        <v>49.48</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.37</v>
+        <v>56.71</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>57.47</v>
+        <v>57.82</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>58.3</v>
+        <v>58.65</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.86</v>
+        <v>58.21</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>81.55</v>
+        <v>82.03</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>88.61</v>
+        <v>89.14</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>116.97</v>
+        <v>117.67</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>59.61</v>
+        <v>59.97</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>67.91</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.87</v>
+        <v>58.22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62.26</v>
+        <v>62.64</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>67.31</v>
+        <v>67.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>75.84999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>59.5</v>
+        <v>59.86</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69.5</v>
+        <v>69.92</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>79.92</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>114.31</v>
+        <v>114.99</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>85.79000000000001</v>
+        <v>86.31</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>91</v>
+        <v>91.55</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>123.04</v>
+        <v>123.77</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>138.37</v>
+        <v>139.2</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>111.24</v>
+        <v>111.9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>121.25</v>
+        <v>121.97</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>129.94</v>
+        <v>130.72</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>133.48</v>
+        <v>134.28</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>165.7</v>
+        <v>166.69</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>192.44</v>
+        <v>193.59</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.15000000000001</v>
+        <v>81.64</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>83.42</v>
+        <v>83.92</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>56.26</v>
+        <v>56.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>63.72</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>81.48</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>99.48</v>
+        <v>100.08</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>77.43000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>96.62</v>
+        <v>97.2</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>91.95999999999999</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>110.34</v>
+        <v>111</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>91.08</v>
+        <v>91.63</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>111.54</v>
+        <v>112.21</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>88.64</v>
+        <v>89.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>103.02</v>
+        <v>103.64</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>108.79</v>
+        <v>109.44</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>111.97</v>
+        <v>112.64</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>89.44</v>
+        <v>89.98</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>101.12</v>
+        <v>101.73</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>48.34</v>
+        <v>48.63</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>48.18</v>
+        <v>48.47</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>87.17</v>
+        <v>87.69</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>96.65000000000001</v>
+        <v>97.23</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>69.42</v>
+        <v>69.84</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>84.53</v>
+        <v>85.03</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>72.63</v>
+        <v>73.06</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>89.08</v>
+        <v>89.61</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>80.28</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97.08</v>
+        <v>97.66</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>52.17</v>
+        <v>52.48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>60.71</v>
+        <v>61.07</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>124.99</v>
+        <v>125.74</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>189.56</v>
+        <v>190.69</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.9</v>
+        <v>62.27</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>101.23</v>
+        <v>101.84</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>57.76</v>
+        <v>58.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>69.66</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>109.56</v>
+        <v>110.22</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>99.95</v>
+        <v>100.55</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>73.92</v>
+        <v>74.36</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>79.02</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>273.83</v>
+        <v>275.47</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>460.08</v>
+        <v>462.84</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.66</v>
+        <v>40.91</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.76</v>
+        <v>50.05</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>33.33</v>
+        <v>33.53</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.89</v>
+        <v>44.15</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.59</v>
+        <v>33.79</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.94</v>
+        <v>43.19</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>40.16</v>
+        <v>40.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.96</v>
+        <v>47.24</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>52.41</v>
+        <v>52.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>59.27</v>
+        <v>59.62</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>45.24</v>
+        <v>45.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50.33</v>
+        <v>50.63</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.97</v>
+        <v>37.19</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.8</v>
+        <v>31.99</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>40.3</v>
+        <v>40.54</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>37.49</v>
+        <v>37.71</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>40.22</v>
+        <v>40.46</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>87.27</v>
+        <v>87.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>62.09</v>
+        <v>62.46</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>47.23</v>
+        <v>47.51</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52.72</v>
+        <v>53.03</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>46.06</v>
+        <v>46.34</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.84</v>
+        <v>52.15</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>42.25</v>
+        <v>42.51</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.51</v>
+        <v>31.7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>36.34</v>
+        <v>36.56</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.5</v>
+        <v>27.66</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>28.14</v>
+        <v>28.3</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>41.03</v>
+        <v>41.28</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>58.26</v>
+        <v>58.61</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>25.25</v>
+        <v>25.4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.91</v>
+        <v>27.08</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.04</v>
+        <v>39.27</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.66</v>
+        <v>42.92</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.98</v>
+        <v>43.24</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>47.11</v>
+        <v>47.4</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>40.53</v>
+        <v>40.77</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.78</v>
+        <v>40.02</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>41.25</v>
+        <v>41.5</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>57.23</v>
+        <v>57.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>60.28</v>
+        <v>60.64</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.67</v>
+        <v>47.96</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.99</v>
+        <v>48.28</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72.33</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.91</v>
+        <v>40.15</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.98</v>
+        <v>51.29</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.72</v>
+        <v>38.95</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.85</v>
+        <v>44.12</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.78</v>
+        <v>48.07</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.35</v>
+        <v>46.63</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>45.1</v>
+        <v>45.37</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.65</v>
+        <v>44.91</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.91</v>
+        <v>38.14</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.97</v>
+        <v>39.2</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>57.66</v>
+        <v>58</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.79</v>
+        <v>55.12</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>52.65</v>
+        <v>52.97</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.74</v>
+        <v>44</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>52.62</v>
+        <v>52.94</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.52</v>
+        <v>61.89</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>48.06</v>
+        <v>48.35</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>50.22</v>
+        <v>50.52</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>56.22</v>
+        <v>56.55</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>85.98</v>
+        <v>86.5</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>97.92</v>
+        <v>98.5</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>68.23999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>70.23</v>
+        <v>70.66</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>56.77</v>
+        <v>57.11</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>59.59</v>
+        <v>59.95</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>62.7</v>
+        <v>63.08</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>72.64</v>
+        <v>73.08</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>73.81</v>
+        <v>74.25</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>67.02</v>
+        <v>67.42</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>81.65000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>65.56</v>
+        <v>65.95</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>66.02</v>
+        <v>66.42</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2602,10 +2602,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>71.23999999999999</v>
+        <v>71.66</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>72.68000000000001</v>
+        <v>73.12</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>64.45</v>
+        <v>64.83</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>66.75</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>63.72</v>
+        <v>64.11</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>70.87</v>
+        <v>71.3</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>71.08</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>73.76000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>73.08</v>
+        <v>73.52</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>71.93000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>64.83</v>
+        <v>65.22</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>69.87</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>59.72</v>
+        <v>60.08</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>63.06</v>
+        <v>63.44</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>54.2</v>
+        <v>54.53</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>65.97</v>
+        <v>66.36</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>74.23</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>52.55</v>
+        <v>52.86</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>52.52</v>
+        <v>52.84</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>48.65</v>
+        <v>48.94</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>41.12</v>
+        <v>41.37</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>61.1</v>
+        <v>61.46</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>60.23</v>
+        <v>60.6</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>62.21</v>
+        <v>62.59</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>63.17</v>
+        <v>63.55</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>52.26</v>
+        <v>52.58</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>53.5</v>
+        <v>53.82</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>50.57</v>
+        <v>50.87</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>56.76</v>
+        <v>57.1</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>59.65</v>
+        <v>60.01</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>60.91</v>
+        <v>61.27</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.7</v>
+        <v>46.98</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>51.48</v>
+        <v>51.78</v>
       </c>
       <c r="F112" s="7" t="inlineStr"/>
     </row>
@@ -3006,10 +3006,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>50.09</v>
+        <v>50.39</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>57.73</v>
+        <v>58.08</v>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
     </row>
@@ -3026,10 +3026,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.83</v>
+        <v>52.14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>55.48</v>
+        <v>55.81</v>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
     </row>
@@ -3046,10 +3046,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>48.03</v>
+        <v>48.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>45.27</v>
+        <v>45.55</v>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.91</v>
+        <v>51.21</v>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
     </row>
@@ -3086,10 +3086,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>62.19</v>
+        <v>62.56</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>61</v>
+        <v>61.37</v>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
     </row>
@@ -3106,10 +3106,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>48.17</v>
+        <v>48.46</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
     </row>
@@ -3126,10 +3126,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>58.37</v>
+        <v>58.72</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.4</v>
+        <v>56.74</v>
       </c>
       <c r="F119" s="7" t="inlineStr"/>
     </row>
@@ -3146,10 +3146,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>54.54</v>
+        <v>54.87</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.83</v>
+        <v>55.16</v>
       </c>
       <c r="F120" s="7" t="inlineStr"/>
     </row>
@@ -3166,10 +3166,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>55.6</v>
+        <v>55.93</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>52.49</v>
+        <v>52.81</v>
       </c>
       <c r="F121" s="7" t="inlineStr"/>
     </row>
@@ -3186,10 +3186,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.63</v>
+        <v>38.86</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
       <c r="F122" s="7" t="inlineStr"/>
     </row>
@@ -3206,10 +3206,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.91</v>
+        <v>44.18</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>51.31</v>
+        <v>51.61</v>
       </c>
       <c r="F123" s="7" t="inlineStr"/>
     </row>
@@ -3226,10 +3226,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>47.46</v>
+        <v>47.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>53.18</v>
+        <v>53.5</v>
       </c>
       <c r="F124" s="7" t="inlineStr"/>
     </row>
@@ -3246,10 +3246,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>43.31</v>
+        <v>43.57</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.99</v>
+        <v>52.3</v>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
     </row>
@@ -3266,10 +3266,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>62.42</v>
+        <v>62.79</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>66.16</v>
+        <v>66.56</v>
       </c>
       <c r="F126" s="7" t="inlineStr"/>
     </row>
@@ -3286,10 +3286,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="F127" s="7" t="inlineStr"/>
     </row>
@@ -3306,10 +3306,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>113.28</v>
+        <v>113.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>116.18</v>
+        <v>116.88</v>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
     </row>
@@ -3326,10 +3326,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>129.84</v>
+        <v>130.62</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>131.29</v>
+        <v>132.08</v>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
     </row>
@@ -3346,10 +3346,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>152.41</v>
+        <v>153.33</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>154.54</v>
+        <v>155.46</v>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
     </row>
@@ -3366,10 +3366,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>224.14</v>
+        <v>225.48</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>221.88</v>
+        <v>223.21</v>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
     </row>
@@ -3386,10 +3386,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>341.67</v>
+        <v>343.72</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>346.88</v>
+        <v>348.96</v>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
     </row>
@@ -3406,10 +3406,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>320.19</v>
+        <v>322.11</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>319.96</v>
+        <v>321.88</v>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
     </row>
@@ -3426,10 +3426,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>61.35</v>
+        <v>61.72</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.87</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>97.72</v>
+        <v>98.31</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>134.87</v>
+        <v>135.68</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>91.34</v>
+        <v>91.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>130.6</v>
+        <v>131.39</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>58.6</v>
+        <v>58.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>78.27</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>61.81</v>
+        <v>62.18</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>70.63</v>
+        <v>71.06</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>44.39</v>
+        <v>44.65</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>56.33</v>
+        <v>56.67</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.13</v>
+        <v>50.43</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.99</v>
+        <v>55.32</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>62.06</v>
+        <v>62.43</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>114.48</v>
+        <v>115.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>121.45</v>
+        <v>122.18</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>125.28</v>
+        <v>126.04</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>138.08</v>
+        <v>138.91</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>150.85</v>
+        <v>151.75</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>155.9</v>
+        <v>156.83</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>173.85</v>
+        <v>174.89</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>170.78</v>
+        <v>171.8</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>142.88</v>
+        <v>143.74</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>157.02</v>
+        <v>157.96</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>137.36</v>
+        <v>138.19</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>145.21</v>
+        <v>146.08</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>166.52</v>
+        <v>167.52</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>128.07</v>
+        <v>128.84</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>146.16</v>
+        <v>147.04</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>107.88</v>
+        <v>108.53</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>99.12</v>
+        <v>99.72</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>123.08</v>
+        <v>123.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>138.21</v>
+        <v>139.04</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>118.8</v>
+        <v>119.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>139.51</v>
+        <v>140.35</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>129.07</v>
+        <v>129.84</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>124.56</v>
+        <v>125.3</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>116.25</v>
+        <v>116.95</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>116.35</v>
+        <v>117.05</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>108.6</v>
+        <v>109.26</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>111.86</v>
+        <v>112.53</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>104.83</v>
+        <v>105.45</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>104.06</v>
+        <v>104.68</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>99.31999999999999</v>
+        <v>99.91</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>103.34</v>
+        <v>103.96</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>95.34999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>58.03</v>
+        <v>58.38</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.7</v>
+        <v>65.09</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>32.34</v>
+        <v>32.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.9</v>
+        <v>41.15</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>78.52</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>97.38</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>122.83</v>
+        <v>123.56</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>131.78</v>
+        <v>132.57</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>110.05</v>
+        <v>110.71</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>113.83</v>
+        <v>114.52</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>93.13</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>91.36</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>189.84</v>
+        <v>190.98</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>210.34</v>
+        <v>211.6</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>173.01</v>
+        <v>174.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>171.6</v>
+        <v>172.63</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>158.44</v>
+        <v>159.39</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>148.36</v>
+        <v>149.25</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>134.15</v>
+        <v>134.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>140.01</v>
+        <v>140.85</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>118.33</v>
+        <v>119.04</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>130.83</v>
+        <v>131.62</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>123.52</v>
+        <v>124.26</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>139.71</v>
+        <v>140.55</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>95.23</v>
+        <v>95.8</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>114.35</v>
+        <v>115.03</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>89.04000000000001</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>104</v>
+        <v>104.62</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>73.11</v>
+        <v>73.55</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>81.18000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>136.32</v>
+        <v>137.14</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>135.31</v>
+        <v>136.12</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>86.26000000000001</v>
+        <v>86.77</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>97.97</v>
+        <v>98.55</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>63.3</v>
+        <v>63.68</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>62.74</v>
+        <v>63.12</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.9</v>
+        <v>49.19</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>44.6</v>
+        <v>44.86</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.53</v>
+        <v>29.71</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.93</v>
+        <v>31.12</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>44.22</v>
+        <v>44.49</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>52.39</v>
+        <v>52.7</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>46.61</v>
+        <v>46.89</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>50.47</v>
+        <v>50.77</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>72.09</v>
+        <v>72.52</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>73.3</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>70.64</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>71.95</v>
+        <v>72.38</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>47.3</v>
+        <v>47.58</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>49.41</v>
+        <v>49.7</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>52.17</v>
+        <v>52.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53.19</v>
+        <v>53.51</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71.98</v>
+        <v>72.41</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>46.05</v>
+        <v>46.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>54.34</v>
+        <v>54.66</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>47.15</v>
+        <v>47.43</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>50.08</v>
+        <v>50.38</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.98</v>
+        <v>46.25</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>38.24</v>
+        <v>38.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.74</v>
+        <v>39.98</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>31.4</v>
+        <v>31.59</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.89</v>
+        <v>36.1</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.99</v>
+        <v>51.3</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>55.64</v>
+        <v>55.97</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>84.94</v>
+        <v>85.45</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>96.04000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.91</v>
+        <v>47.19</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>26.32</v>
+        <v>26.47</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>31.21</v>
+        <v>31.39</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>20.2</v>
+        <v>20.32</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>27.08</v>
+        <v>27.25</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.42</v>
+        <v>11.49</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.9</v>
+        <v>11.97</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>38.51</v>
+        <v>38.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.7</v>
+        <v>40.95</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.19</v>
+        <v>60.55</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>61.29</v>
+        <v>61.66</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>80.14</v>
+        <v>80.62</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>85.95</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93</v>
+        <v>93.55</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>88.44</v>
+        <v>88.97</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>93.12</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>165.97</v>
+        <v>166.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>193.85</v>
+        <v>195.02</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>253.66</v>
+        <v>255.19</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>282.59</v>
+        <v>284.29</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>332.94</v>
+        <v>334.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>444.11</v>
+        <v>446.77</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>372.56</v>
+        <v>374.8</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>422.72</v>
+        <v>425.25</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>171.49</v>
+        <v>172.52</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>194.64</v>
+        <v>195.81</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>151.34</v>
+        <v>152.25</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>171.91</v>
+        <v>172.94</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>138.24</v>
+        <v>139.07</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>143.63</v>
+        <v>144.49</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>113.73</v>
+        <v>114.41</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>129.3</v>
+        <v>130.08</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>85.48</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>75.43000000000001</v>
+        <v>75.88</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>96.8</v>
+        <v>97.38</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>90.45</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.05</v>
+        <v>85.56</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>79.91</v>
+        <v>80.39</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>77.13</v>
+        <v>77.59</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>78.14</v>
+        <v>78.61</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>92.42</v>
+        <v>92.98</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>95.04000000000001</v>
+        <v>95.61</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.66</v>
+        <v>41.91</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>57.31</v>
+        <v>57.65</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.44</v>
+        <v>25.59</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.69</v>
+        <v>35.91</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.92</v>
+        <v>41.16</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>41.22</v>
+        <v>41.47</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.92</v>
+        <v>29.09</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.94</v>
+        <v>27.1</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.69</v>
+        <v>40.93</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.97</v>
+        <v>62.34</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>56.04</v>
+        <v>56.38</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.77</v>
+        <v>53.09</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.75</v>
+        <v>54.08</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>53.14</v>
+        <v>53.46</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>87.53</v>
+        <v>88.05</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>117.82</v>
+        <v>118.52</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>74.23999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>72.39</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>77.91</v>
+        <v>78.38</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>149.28</v>
+        <v>150.18</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>154.16</v>
+        <v>155.09</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>188.03</v>
+        <v>189.16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>224.61</v>
+        <v>225.96</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>190.54</v>
+        <v>191.68</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>227.3</v>
+        <v>228.66</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>135.55</v>
+        <v>136.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>164.57</v>
+        <v>165.56</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.69</v>
+        <v>23.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.89</v>
+        <v>33.09</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>52.38</v>
+        <v>52.7</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>55.25</v>
+        <v>55.58</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>100.77</v>
+        <v>101.37</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>101.52</v>
+        <v>102.13</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>79.95</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>71.94</v>
+        <v>72.37</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>119</v>
+        <v>119.72</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>114.24</v>
+        <v>114.92</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>127.06</v>
+        <v>127.82</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>130.52</v>
+        <v>131.31</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>104.14</v>
+        <v>104.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>104.96</v>
+        <v>105.59</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>104.39</v>
+        <v>105.01</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>102.36</v>
+        <v>102.98</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>107.09</v>
+        <v>107.73</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>117.43</v>
+        <v>118.13</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>226.63</v>
+        <v>227.99</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>338.89</v>
+        <v>340.92</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>121.23</v>
+        <v>121.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>134.19</v>
+        <v>135</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>128.25</v>
+        <v>129.02</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>136.79</v>
+        <v>137.61</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>29.2</v>
+        <v>29.37</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.96</v>
+        <v>37.18</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.99</v>
+        <v>25.14</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.36</v>
+        <v>27.52</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>41.15</v>
+        <v>41.39</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.88</v>
+        <v>35.09</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>60.16</v>
+        <v>60.52</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>101.85</v>
+        <v>102.46</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>115.93</v>
+        <v>116.62</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.69</v>
+        <v>91.23</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>88.52</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.77</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>88.52</v>
+        <v>89.05</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>85.3</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>82.45</v>
+        <v>82.78</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>85.3</v>
+        <v>85.64</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>93.59</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>90.81999999999999</v>
+        <v>91</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>93.59</v>
+        <v>93.78</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5872,6 +5872,26 @@
         <v>122.76</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="F257" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5884,7 +5904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5934,10 +5954,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>545.26</v>
+        <v>548.53</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>696.66</v>
+        <v>700.84</v>
       </c>
     </row>
     <row r="3">
@@ -5953,10 +5973,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>139.44</v>
+        <v>140.27</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="4">
@@ -5972,10 +5992,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>198.56</v>
+        <v>199.75</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>204.04</v>
+        <v>205.26</v>
       </c>
     </row>
     <row r="5">
@@ -5991,10 +6011,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>188.85</v>
+        <v>189.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>248.52</v>
+        <v>250.01</v>
       </c>
     </row>
     <row r="6">
@@ -6010,10 +6030,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>121.77</v>
+        <v>122.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137.06</v>
+        <v>137.89</v>
       </c>
     </row>
     <row r="7">
@@ -6029,10 +6049,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>144.4</v>
+        <v>145.27</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>179.25</v>
+        <v>180.32</v>
       </c>
     </row>
     <row r="8">
@@ -6048,10 +6068,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100.86</v>
+        <v>101.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>103.71</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="9">
@@ -6067,10 +6087,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>74.8</v>
+        <v>75.25</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="10">
@@ -6086,10 +6106,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>64.27</v>
+        <v>64.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>70.31999999999999</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6105,10 +6125,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56.34</v>
+        <v>56.68</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.11</v>
+        <v>62.48</v>
       </c>
     </row>
     <row r="12">
@@ -6124,10 +6144,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>49.19</v>
+        <v>49.48</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>56.37</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="13">
@@ -6143,10 +6163,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>57.47</v>
+        <v>57.82</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>58.3</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="14">
@@ -6162,10 +6182,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.86</v>
+        <v>58.21</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>81.55</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="15">
@@ -6181,10 +6201,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>88.61</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="16">
@@ -6200,10 +6220,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>116.97</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="17">
@@ -6219,10 +6239,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>59.61</v>
+        <v>59.97</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="18">
@@ -6238,10 +6258,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -6257,10 +6277,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.87</v>
+        <v>58.22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>62.26</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="20">
@@ -6276,10 +6296,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>67.31</v>
+        <v>67.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>75.84999999999999</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="21">
@@ -6295,10 +6315,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>59.5</v>
+        <v>59.86</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69.5</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="22">
@@ -6314,10 +6334,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>79.92</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -6333,10 +6353,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>114.31</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="24">
@@ -6352,10 +6372,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>85.79000000000001</v>
+        <v>86.31</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>91</v>
+        <v>91.55</v>
       </c>
     </row>
     <row r="25">
@@ -6371,10 +6391,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>123.04</v>
+        <v>123.77</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>138.37</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="26">
@@ -6390,10 +6410,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>111.24</v>
+        <v>111.9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>121.25</v>
+        <v>121.97</v>
       </c>
     </row>
     <row r="27">
@@ -6409,10 +6429,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>129.94</v>
+        <v>130.72</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>133.48</v>
+        <v>134.28</v>
       </c>
     </row>
     <row r="28">
@@ -6428,10 +6448,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>165.7</v>
+        <v>166.69</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>192.44</v>
+        <v>193.59</v>
       </c>
     </row>
     <row r="29">
@@ -6447,10 +6467,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>81.15000000000001</v>
+        <v>81.64</v>
       </c>
     </row>
     <row r="30">
@@ -6466,10 +6486,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>83.42</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="31">
@@ -6485,10 +6505,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>56.26</v>
+        <v>56.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>63.72</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -6504,10 +6524,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>81.48</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -6523,10 +6543,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>99.48</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="34">
@@ -6542,10 +6562,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>77.43000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>96.62</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="35">
@@ -6561,10 +6581,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>91.95999999999999</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>110.34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
@@ -6580,10 +6600,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>91.08</v>
+        <v>91.63</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>111.54</v>
+        <v>112.21</v>
       </c>
     </row>
     <row r="37">
@@ -6599,10 +6619,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>88.64</v>
+        <v>89.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>103.02</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="38">
@@ -6618,10 +6638,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>108.79</v>
+        <v>109.44</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>111.97</v>
+        <v>112.64</v>
       </c>
     </row>
     <row r="39">
@@ -6637,10 +6657,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>89.44</v>
+        <v>89.98</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>101.12</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="40">
@@ -6656,10 +6676,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>48.34</v>
+        <v>48.63</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>48.18</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="41">
@@ -6675,10 +6695,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>87.17</v>
+        <v>87.69</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>96.65000000000001</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="42">
@@ -6694,10 +6714,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>69.42</v>
+        <v>69.84</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>84.53</v>
+        <v>85.03</v>
       </c>
     </row>
     <row r="43">
@@ -6713,10 +6733,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>72.63</v>
+        <v>73.06</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>89.08</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="44">
@@ -6732,10 +6752,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>80.28</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97.08</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="45">
@@ -6751,10 +6771,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>52.17</v>
+        <v>52.48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>60.71</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="46">
@@ -6770,10 +6790,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>124.99</v>
+        <v>125.74</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>189.56</v>
+        <v>190.69</v>
       </c>
     </row>
     <row r="47">
@@ -6789,10 +6809,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.9</v>
+        <v>62.27</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>101.23</v>
+        <v>101.84</v>
       </c>
     </row>
     <row r="48">
@@ -6808,10 +6828,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>57.76</v>
+        <v>58.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="49">
@@ -6827,10 +6847,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>109.56</v>
+        <v>110.22</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>99.95</v>
+        <v>100.55</v>
       </c>
     </row>
     <row r="50">
@@ -6846,10 +6866,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>73.92</v>
+        <v>74.36</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>79.02</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -6865,10 +6885,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>273.83</v>
+        <v>275.47</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>460.08</v>
+        <v>462.84</v>
       </c>
     </row>
     <row r="52">
@@ -6884,10 +6904,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.66</v>
+        <v>40.91</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.76</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="53">
@@ -6903,10 +6923,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>33.33</v>
+        <v>33.53</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.89</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="54">
@@ -6922,10 +6942,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.59</v>
+        <v>33.79</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.94</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="55">
@@ -6941,10 +6961,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>40.16</v>
+        <v>40.41</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.96</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="56">
@@ -6960,10 +6980,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>52.41</v>
+        <v>52.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>59.27</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="57">
@@ -6979,10 +6999,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>49.46</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="58">
@@ -6998,10 +7018,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>45.24</v>
+        <v>45.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50.33</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="59">
@@ -7017,10 +7037,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.97</v>
+        <v>37.19</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.8</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="60">
@@ -7036,10 +7056,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>40.3</v>
+        <v>40.54</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="61">
@@ -7055,10 +7075,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>37.49</v>
+        <v>37.71</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>40.22</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="62">
@@ -7074,10 +7094,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>87.27</v>
+        <v>87.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>62.09</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="63">
@@ -7093,10 +7113,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>47.23</v>
+        <v>47.51</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52.72</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="64">
@@ -7112,10 +7132,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>46.06</v>
+        <v>46.34</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.84</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="65">
@@ -7131,10 +7151,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>42.25</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="66">
@@ -7150,10 +7170,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.51</v>
+        <v>31.7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>36.34</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="67">
@@ -7169,10 +7189,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.5</v>
+        <v>27.66</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>28.14</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="68">
@@ -7188,10 +7208,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>41.03</v>
+        <v>41.28</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>58.26</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="69">
@@ -7207,10 +7227,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>25.25</v>
+        <v>25.4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.91</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="70">
@@ -7226,10 +7246,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.04</v>
+        <v>39.27</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.66</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="71">
@@ -7245,10 +7265,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.98</v>
+        <v>43.24</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>47.11</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="72">
@@ -7264,10 +7284,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>40.53</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="73">
@@ -7283,10 +7303,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.78</v>
+        <v>40.02</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>41.25</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="74">
@@ -7302,10 +7322,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>57.23</v>
+        <v>57.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>60.28</v>
+        <v>60.64</v>
       </c>
     </row>
     <row r="75">
@@ -7321,10 +7341,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.67</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="76">
@@ -7340,10 +7360,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.99</v>
+        <v>48.28</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72.33</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7359,10 +7379,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.91</v>
+        <v>40.15</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.98</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="78">
@@ -7378,10 +7398,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.72</v>
+        <v>38.95</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.85</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="79">
@@ -7397,10 +7417,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.78</v>
+        <v>48.07</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.35</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="80">
@@ -7416,10 +7436,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>45.1</v>
+        <v>45.37</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.65</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="81">
@@ -7435,10 +7455,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.91</v>
+        <v>38.14</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.97</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="82">
@@ -7454,10 +7474,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>57.66</v>
+        <v>58</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="83">
@@ -7473,10 +7493,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.79</v>
+        <v>55.12</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="84">
@@ -7492,10 +7512,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>52.65</v>
+        <v>52.97</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
@@ -7511,10 +7531,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>52.62</v>
+        <v>52.94</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.52</v>
+        <v>61.89</v>
       </c>
     </row>
     <row r="86">
@@ -7530,10 +7550,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>48.06</v>
+        <v>48.35</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="87">
@@ -7549,10 +7569,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>50.22</v>
+        <v>50.52</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>56.22</v>
+        <v>56.55</v>
       </c>
     </row>
     <row r="88">
@@ -7568,10 +7588,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>85.98</v>
+        <v>86.5</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>97.92</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="89">
@@ -7587,10 +7607,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>68.23999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>70.23</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="90">
@@ -7606,10 +7626,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>56.77</v>
+        <v>57.11</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>59.59</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="91">
@@ -7625,10 +7645,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>62.7</v>
+        <v>63.08</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>64.64</v>
+        <v>65.03</v>
       </c>
     </row>
     <row r="92">
@@ -7644,10 +7664,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>72.64</v>
+        <v>73.08</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>73.81</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="93">
@@ -7663,10 +7683,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>67.02</v>
+        <v>67.42</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94">
@@ -7682,10 +7702,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>81.65000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -7701,10 +7721,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>65.56</v>
+        <v>65.95</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>66.02</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="96">
@@ -7720,10 +7740,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>71.23999999999999</v>
+        <v>71.66</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>72.68000000000001</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="97">
@@ -7739,10 +7759,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>64.45</v>
+        <v>64.83</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>66.75</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -7758,10 +7778,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>63.72</v>
+        <v>64.11</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>70.87</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="99">
@@ -7777,10 +7797,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>71.08</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>73.76000000000001</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="100">
@@ -7796,10 +7816,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>73.08</v>
+        <v>73.52</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>71.93000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="101">
@@ -7815,10 +7835,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>64.83</v>
+        <v>65.22</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>69.87</v>
+        <v>70.29000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7834,10 +7854,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>59.72</v>
+        <v>60.08</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>63.06</v>
+        <v>63.44</v>
       </c>
     </row>
     <row r="103">
@@ -7853,10 +7873,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>54.2</v>
+        <v>54.53</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="104">
@@ -7872,10 +7892,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>65.97</v>
+        <v>66.36</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>74.23</v>
+        <v>74.68000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7891,10 +7911,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>52.55</v>
+        <v>52.86</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>52.52</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="106">
@@ -7910,10 +7930,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>48.65</v>
+        <v>48.94</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.12</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="107">
@@ -7929,10 +7949,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>61.1</v>
+        <v>61.46</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>60.23</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="108">
@@ -7948,10 +7968,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>62.21</v>
+        <v>62.59</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>63.17</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="109">
@@ -7967,10 +7987,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>52.26</v>
+        <v>52.58</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>53.5</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="110">
@@ -7986,10 +8006,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>50.57</v>
+        <v>50.87</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>56.76</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="111">
@@ -8005,10 +8025,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>59.65</v>
+        <v>60.01</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>60.91</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="112">
@@ -8024,10 +8044,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.7</v>
+        <v>46.98</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>51.48</v>
+        <v>51.78</v>
       </c>
     </row>
     <row r="113">
@@ -8043,10 +8063,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>50.09</v>
+        <v>50.39</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>57.73</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="114">
@@ -8062,10 +8082,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.83</v>
+        <v>52.14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>55.48</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="115">
@@ -8081,10 +8101,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>48.03</v>
+        <v>48.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>45.27</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="116">
@@ -8100,10 +8120,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.91</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="117">
@@ -8119,10 +8139,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>62.19</v>
+        <v>62.56</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>61</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="118">
@@ -8138,10 +8158,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>48.17</v>
+        <v>48.46</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="119">
@@ -8157,10 +8177,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>58.37</v>
+        <v>58.72</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.4</v>
+        <v>56.74</v>
       </c>
     </row>
     <row r="120">
@@ -8176,10 +8196,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>54.54</v>
+        <v>54.87</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.83</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="121">
@@ -8195,10 +8215,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>55.6</v>
+        <v>55.93</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>52.49</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="122">
@@ -8214,10 +8234,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.63</v>
+        <v>38.86</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>50.53</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="123">
@@ -8233,10 +8253,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.91</v>
+        <v>44.18</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>51.31</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="124">
@@ -8252,10 +8272,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>47.46</v>
+        <v>47.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>53.18</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="125">
@@ -8271,10 +8291,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>43.31</v>
+        <v>43.57</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.99</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="126">
@@ -8290,10 +8310,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>62.42</v>
+        <v>62.79</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>66.16</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="127">
@@ -8309,10 +8329,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>82.23</v>
       </c>
     </row>
     <row r="128">
@@ -8328,10 +8348,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>113.28</v>
+        <v>113.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>116.18</v>
+        <v>116.88</v>
       </c>
     </row>
     <row r="129">
@@ -8347,10 +8367,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>129.84</v>
+        <v>130.62</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>131.29</v>
+        <v>132.08</v>
       </c>
     </row>
     <row r="130">
@@ -8366,10 +8386,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>152.41</v>
+        <v>153.33</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>154.54</v>
+        <v>155.46</v>
       </c>
     </row>
     <row r="131">
@@ -8385,10 +8405,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>224.14</v>
+        <v>225.48</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>221.88</v>
+        <v>223.21</v>
       </c>
     </row>
     <row r="132">
@@ -8404,10 +8424,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>341.67</v>
+        <v>343.72</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>346.88</v>
+        <v>348.96</v>
       </c>
     </row>
     <row r="133">
@@ -8423,10 +8443,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>320.19</v>
+        <v>322.11</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>319.96</v>
+        <v>321.88</v>
       </c>
     </row>
     <row r="134">
@@ -8442,10 +8462,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>61.35</v>
+        <v>61.72</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.87</v>
       </c>
     </row>
     <row r="135">
@@ -8461,10 +8481,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>97.72</v>
+        <v>98.31</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>134.87</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="136">
@@ -8480,10 +8500,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>91.34</v>
+        <v>91.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>130.6</v>
+        <v>131.39</v>
       </c>
     </row>
     <row r="137">
@@ -8499,10 +8519,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>58.6</v>
+        <v>58.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>78.27</v>
+        <v>78.73999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -8518,10 +8538,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>61.81</v>
+        <v>62.18</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>70.63</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="139">
@@ -8537,10 +8557,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>44.39</v>
+        <v>44.65</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>56.33</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="140">
@@ -8556,10 +8576,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.13</v>
+        <v>50.43</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="141">
@@ -8575,10 +8595,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.99</v>
+        <v>55.32</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>62.06</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="142">
@@ -8594,10 +8614,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>114.48</v>
+        <v>115.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>121.45</v>
+        <v>122.18</v>
       </c>
     </row>
     <row r="143">
@@ -8613,10 +8633,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>125.28</v>
+        <v>126.04</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>138.08</v>
+        <v>138.91</v>
       </c>
     </row>
     <row r="144">
@@ -8632,10 +8652,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>150.85</v>
+        <v>151.75</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>155.9</v>
+        <v>156.83</v>
       </c>
     </row>
     <row r="145">
@@ -8651,10 +8671,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>173.85</v>
+        <v>174.89</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>170.78</v>
+        <v>171.8</v>
       </c>
     </row>
     <row r="146">
@@ -8670,10 +8690,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>142.88</v>
+        <v>143.74</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>157.02</v>
+        <v>157.96</v>
       </c>
     </row>
     <row r="147">
@@ -8689,10 +8709,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>137.36</v>
+        <v>138.19</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>145.21</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="148">
@@ -8708,10 +8728,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>153.18</v>
+        <v>154.1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>166.52</v>
+        <v>167.52</v>
       </c>
     </row>
     <row r="149">
@@ -8727,10 +8747,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>128.07</v>
+        <v>128.84</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>146.16</v>
+        <v>147.04</v>
       </c>
     </row>
     <row r="150">
@@ -8746,10 +8766,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>107.88</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="151">
@@ -8765,10 +8785,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>99.12</v>
+        <v>99.72</v>
       </c>
     </row>
     <row r="152">
@@ -8784,10 +8804,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>123.08</v>
+        <v>123.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>138.21</v>
+        <v>139.04</v>
       </c>
     </row>
     <row r="153">
@@ -8803,10 +8823,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>118.8</v>
+        <v>119.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>139.51</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="154">
@@ -8822,10 +8842,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>129.07</v>
+        <v>129.84</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>124.56</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="155">
@@ -8841,10 +8861,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>116.25</v>
+        <v>116.95</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>116.35</v>
+        <v>117.05</v>
       </c>
     </row>
     <row r="156">
@@ -8860,10 +8880,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>108.6</v>
+        <v>109.26</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>111.86</v>
+        <v>112.53</v>
       </c>
     </row>
     <row r="157">
@@ -8879,10 +8899,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>104.83</v>
+        <v>105.45</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>104.06</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="158">
@@ -8898,10 +8918,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>99.31999999999999</v>
+        <v>99.91</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>103.34</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="159">
@@ -8917,10 +8937,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>95.34999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
     </row>
     <row r="160">
@@ -8936,10 +8956,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>58.03</v>
+        <v>58.38</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.7</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="161">
@@ -8955,10 +8975,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>32.34</v>
+        <v>32.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.9</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="162">
@@ -8974,10 +8994,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>78.52</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>97.38</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -8993,10 +9013,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>122.83</v>
+        <v>123.56</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>131.78</v>
+        <v>132.57</v>
       </c>
     </row>
     <row r="164">
@@ -9012,10 +9032,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>110.05</v>
+        <v>110.71</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>113.83</v>
+        <v>114.52</v>
       </c>
     </row>
     <row r="165">
@@ -9031,10 +9051,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>93.13</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>91.36</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9050,10 +9070,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>189.84</v>
+        <v>190.98</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>210.34</v>
+        <v>211.6</v>
       </c>
     </row>
     <row r="167">
@@ -9069,10 +9089,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>173.01</v>
+        <v>174.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>171.6</v>
+        <v>172.63</v>
       </c>
     </row>
     <row r="168">
@@ -9088,10 +9108,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>158.44</v>
+        <v>159.39</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>148.36</v>
+        <v>149.25</v>
       </c>
     </row>
     <row r="169">
@@ -9107,10 +9127,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>134.15</v>
+        <v>134.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>140.01</v>
+        <v>140.85</v>
       </c>
     </row>
     <row r="170">
@@ -9126,10 +9146,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>118.33</v>
+        <v>119.04</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>130.83</v>
+        <v>131.62</v>
       </c>
     </row>
     <row r="171">
@@ -9145,10 +9165,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>123.52</v>
+        <v>124.26</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>139.71</v>
+        <v>140.55</v>
       </c>
     </row>
     <row r="172">
@@ -9164,10 +9184,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>95.23</v>
+        <v>95.8</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>114.35</v>
+        <v>115.03</v>
       </c>
     </row>
     <row r="173">
@@ -9183,10 +9203,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>89.04000000000001</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>104</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="174">
@@ -9202,10 +9222,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>73.11</v>
+        <v>73.55</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>81.18000000000001</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="175">
@@ -9221,10 +9241,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>136.32</v>
+        <v>137.14</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>135.31</v>
+        <v>136.12</v>
       </c>
     </row>
     <row r="176">
@@ -9240,10 +9260,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>86.26000000000001</v>
+        <v>86.77</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>97.97</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="177">
@@ -9259,10 +9279,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>63.3</v>
+        <v>63.68</v>
       </c>
     </row>
     <row r="178">
@@ -9278,10 +9298,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>62.74</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="179">
@@ -9297,10 +9317,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.9</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="180">
@@ -9316,10 +9336,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>44.6</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="181">
@@ -9335,10 +9355,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.53</v>
+        <v>29.71</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.93</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="182">
@@ -9354,10 +9374,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>44.22</v>
+        <v>44.49</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>52.39</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="183">
@@ -9373,10 +9393,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>46.61</v>
+        <v>46.89</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>50.47</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="184">
@@ -9392,10 +9412,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>72.09</v>
+        <v>72.52</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>73.3</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9411,10 +9431,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>70.64</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>71.95</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="186">
@@ -9430,10 +9450,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>47.3</v>
+        <v>47.58</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>49.41</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="187">
@@ -9449,10 +9469,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>52.17</v>
+        <v>52.49</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53.19</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="188">
@@ -9468,10 +9488,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71.98</v>
+        <v>72.41</v>
       </c>
     </row>
     <row r="189">
@@ -9487,10 +9507,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>46.05</v>
+        <v>46.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>54.34</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="190">
@@ -9506,10 +9526,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>47.15</v>
+        <v>47.43</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>50.08</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="191">
@@ -9525,10 +9545,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.98</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="192">
@@ -9544,10 +9564,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>38.24</v>
+        <v>38.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.74</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="193">
@@ -9563,10 +9583,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>31.4</v>
+        <v>31.59</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.89</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="194">
@@ -9582,10 +9602,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.99</v>
+        <v>51.3</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>55.64</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="195">
@@ -9601,10 +9621,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>84.94</v>
+        <v>85.45</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>96.04000000000001</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="196">
@@ -9620,10 +9640,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.91</v>
+        <v>47.19</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="197">
@@ -9639,10 +9659,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>26.32</v>
+        <v>26.47</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>31.21</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="198">
@@ -9658,10 +9678,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>20.2</v>
+        <v>20.32</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>27.08</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="199">
@@ -9677,10 +9697,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.42</v>
+        <v>11.49</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.9</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="200">
@@ -9696,10 +9716,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>38.51</v>
+        <v>38.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.7</v>
+        <v>40.95</v>
       </c>
     </row>
     <row r="201">
@@ -9715,10 +9735,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.19</v>
+        <v>60.55</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>61.29</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="202">
@@ -9734,10 +9754,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>80.14</v>
+        <v>80.62</v>
       </c>
     </row>
     <row r="203">
@@ -9753,10 +9773,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>85.95</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>93</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="204">
@@ -9772,10 +9792,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>88.44</v>
+        <v>88.97</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>93.12</v>
+        <v>93.68000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -9791,10 +9811,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>165.97</v>
+        <v>166.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>193.85</v>
+        <v>195.02</v>
       </c>
     </row>
     <row r="206">
@@ -9810,10 +9830,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>253.66</v>
+        <v>255.19</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>282.59</v>
+        <v>284.29</v>
       </c>
     </row>
     <row r="207">
@@ -9829,10 +9849,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>332.94</v>
+        <v>334.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>444.11</v>
+        <v>446.77</v>
       </c>
     </row>
     <row r="208">
@@ -9848,10 +9868,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>372.56</v>
+        <v>374.8</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>422.72</v>
+        <v>425.25</v>
       </c>
     </row>
     <row r="209">
@@ -9867,10 +9887,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>171.49</v>
+        <v>172.52</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>194.64</v>
+        <v>195.81</v>
       </c>
     </row>
     <row r="210">
@@ -9886,10 +9906,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>151.34</v>
+        <v>152.25</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>171.91</v>
+        <v>172.94</v>
       </c>
     </row>
     <row r="211">
@@ -9905,10 +9925,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>138.24</v>
+        <v>139.07</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>143.63</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="212">
@@ -9924,10 +9944,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>113.73</v>
+        <v>114.41</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>129.3</v>
+        <v>130.08</v>
       </c>
     </row>
     <row r="213">
@@ -9943,10 +9963,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>85.48</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>75.43000000000001</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="214">
@@ -9962,10 +9982,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>96.8</v>
+        <v>97.38</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="215">
@@ -9981,10 +10001,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>90.45</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.05</v>
+        <v>85.56</v>
       </c>
     </row>
     <row r="216">
@@ -10000,10 +10020,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>79.91</v>
+        <v>80.39</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="217">
@@ -10019,10 +10039,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>77.13</v>
+        <v>77.59</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>78.14</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="218">
@@ -10038,10 +10058,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>92.42</v>
+        <v>92.98</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>95.04000000000001</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="219">
@@ -10057,10 +10077,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.66</v>
+        <v>41.91</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>57.31</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="220">
@@ -10076,10 +10096,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.44</v>
+        <v>25.59</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.69</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="221">
@@ -10095,10 +10115,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.92</v>
+        <v>41.16</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>41.22</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="222">
@@ -10114,10 +10134,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.92</v>
+        <v>29.09</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.94</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="223">
@@ -10133,10 +10153,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.69</v>
+        <v>40.93</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="224">
@@ -10152,10 +10172,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.97</v>
+        <v>62.34</v>
       </c>
     </row>
     <row r="225">
@@ -10171,10 +10191,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>56.04</v>
+        <v>56.38</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.77</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="226">
@@ -10190,10 +10210,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.75</v>
+        <v>54.08</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>53.14</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="227">
@@ -10209,10 +10229,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>87.53</v>
+        <v>88.05</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>117.82</v>
+        <v>118.52</v>
       </c>
     </row>
     <row r="228">
@@ -10228,10 +10248,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>74.23999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="229">
@@ -10247,10 +10267,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>77.91</v>
+        <v>78.38</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>74.97</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="230">
@@ -10266,10 +10286,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>149.28</v>
+        <v>150.18</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>154.16</v>
+        <v>155.09</v>
       </c>
     </row>
     <row r="231">
@@ -10285,10 +10305,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>188.03</v>
+        <v>189.16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>224.61</v>
+        <v>225.96</v>
       </c>
     </row>
     <row r="232">
@@ -10304,10 +10324,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>190.54</v>
+        <v>191.68</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>227.3</v>
+        <v>228.66</v>
       </c>
     </row>
     <row r="233">
@@ -10323,10 +10343,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>135.55</v>
+        <v>136.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>164.57</v>
+        <v>165.56</v>
       </c>
     </row>
     <row r="234">
@@ -10342,10 +10362,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.69</v>
+        <v>23.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.89</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="235">
@@ -10361,10 +10381,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>52.38</v>
+        <v>52.7</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>55.25</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="236">
@@ -10380,10 +10400,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>100.77</v>
+        <v>101.37</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>101.52</v>
+        <v>102.13</v>
       </c>
     </row>
     <row r="237">
@@ -10399,10 +10419,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>79.95</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>71.94</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="238">
@@ -10418,10 +10438,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>119</v>
+        <v>119.72</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>114.24</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="239">
@@ -10437,10 +10457,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>127.06</v>
+        <v>127.82</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>130.52</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="240">
@@ -10456,10 +10476,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>104.14</v>
+        <v>104.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>104.96</v>
+        <v>105.59</v>
       </c>
     </row>
     <row r="241">
@@ -10475,10 +10495,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>104.39</v>
+        <v>105.01</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>102.36</v>
+        <v>102.98</v>
       </c>
     </row>
     <row r="242">
@@ -10494,10 +10514,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>107.09</v>
+        <v>107.73</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>117.43</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="243">
@@ -10513,10 +10533,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>226.63</v>
+        <v>227.99</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>338.89</v>
+        <v>340.92</v>
       </c>
     </row>
     <row r="244">
@@ -10532,10 +10552,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>121.23</v>
+        <v>121.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>134.19</v>
+        <v>135</v>
       </c>
     </row>
     <row r="245">
@@ -10551,10 +10571,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>128.25</v>
+        <v>129.02</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>136.79</v>
+        <v>137.61</v>
       </c>
     </row>
     <row r="246">
@@ -10570,10 +10590,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>29.2</v>
+        <v>29.37</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.96</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="247">
@@ -10589,10 +10609,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.99</v>
+        <v>25.14</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.36</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="248">
@@ -10608,10 +10628,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>41.15</v>
+        <v>41.39</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.88</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="249">
@@ -10627,10 +10647,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>60.16</v>
+        <v>60.52</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="250">
@@ -10646,10 +10666,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>101.85</v>
+        <v>102.46</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>115.93</v>
+        <v>116.62</v>
       </c>
     </row>
     <row r="251">
@@ -10665,10 +10685,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.69</v>
+        <v>91.23</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.48999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10684,10 +10704,10 @@
         <v>88.52</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.77</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>88.52</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="253">
@@ -10703,10 +10723,10 @@
         <v>85.3</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>82.45</v>
+        <v>82.78</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>85.3</v>
+        <v>85.64</v>
       </c>
     </row>
     <row r="254">
@@ -10722,10 +10742,10 @@
         <v>93.59</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>90.81999999999999</v>
+        <v>91</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>93.59</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="255">
@@ -10766,8 +10786,27 @@
         <v>122.76</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>76.94</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B256">
+  <conditionalFormatting sqref="B2:B257">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10779,7 +10818,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C256">
+  <conditionalFormatting sqref="C2:C257">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10791,7 +10830,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D256">
+  <conditionalFormatting sqref="D2:D257">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10803,7 +10842,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E256">
+  <conditionalFormatting sqref="E2:E257">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
